--- a/URUVS/Datasheets/URUV/03.2024/March_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/03.2024/March_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sophi\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\03.2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\03.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B01C3BA-A485-4E3B-A221-D8A5F73F500F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1427E9E4-8EE6-4AC8-B23E-A89F7326A867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="MetaData" sheetId="3" r:id="rId3"/>
     <sheet name="LATLON" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,6 +26,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="224">
   <si>
     <t>DATE</t>
   </si>
@@ -660,6 +666,51 @@
   </si>
   <si>
     <t>MARCH</t>
+  </si>
+  <si>
+    <t>MAXN_MUDCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STMUDCRAB</t>
+  </si>
+  <si>
+    <t>T1_MUDCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STSWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>T1_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_FISHO</t>
+  </si>
+  <si>
+    <t>TIME_1STFISHO</t>
+  </si>
+  <si>
+    <t>T1_FISHO</t>
+  </si>
+  <si>
+    <t>MAXN_SHRIMP</t>
+  </si>
+  <si>
+    <t>TIME_1STSHRIMP</t>
+  </si>
+  <si>
+    <t>T1_SHRIMP</t>
+  </si>
+  <si>
+    <t>MAXN_ULAR</t>
+  </si>
+  <si>
+    <t>TIME_1STULAR</t>
+  </si>
+  <si>
+    <t>T1_ULAR</t>
   </si>
 </sst>
 </file>
@@ -896,15 +947,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -917,8 +968,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -930,9 +981,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="21" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -940,7 +991,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -948,16 +998,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -966,10 +1016,10 @@
     <xf numFmtId="46" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -984,7 +1034,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -997,12 +1047,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1016,17 +1062,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="21" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="21" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1307,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:DC22"/>
+  <dimension ref="A1:DR22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -1324,17 +1364,20 @@
     <col min="52" max="52" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="8.7265625" style="88"/>
     <col min="79" max="79" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="88" max="88" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="103" max="103" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="106" max="106" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:107" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:122" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>207</v>
       </c>
@@ -1407,7 +1450,7 @@
       <c r="X1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="82" t="s">
+      <c r="Y1" s="77" t="s">
         <v>15</v>
       </c>
       <c r="Z1" s="16" t="s">
@@ -1563,7 +1606,7 @@
       <c r="BX1" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="BY1" s="85" t="s">
+      <c r="BY1" s="27" t="s">
         <v>181</v>
       </c>
       <c r="BZ1" s="28" t="s">
@@ -1578,86 +1621,131 @@
       <c r="CC1" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="CD1" s="72" t="s">
+      <c r="CD1" s="67" t="s">
         <v>195</v>
       </c>
       <c r="CE1" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="CF1" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="CG1" s="67" t="s">
+        <v>217</v>
+      </c>
+      <c r="CH1" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="CF1" s="28" t="s">
+      <c r="CI1" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="CG1" s="72" t="s">
+      <c r="CJ1" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="CH1" s="27" t="s">
+      <c r="CK1" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="CI1" s="28" t="s">
+      <c r="CL1" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="CJ1" s="72" t="s">
+      <c r="CM1" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="CK1" s="27" t="s">
+      <c r="CN1" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="CL1" s="28" t="s">
+      <c r="CO1" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="CM1" s="72" t="s">
+      <c r="CP1" s="67" t="s">
         <v>189</v>
       </c>
-      <c r="CN1" s="27" t="s">
+      <c r="CQ1" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="CO1" s="28" t="s">
+      <c r="CR1" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="CP1" s="72" t="s">
+      <c r="CS1" s="67" t="s">
         <v>192</v>
       </c>
-      <c r="CQ1" s="27" t="s">
+      <c r="CT1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="CR1" s="28" t="s">
+      <c r="CU1" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="CS1" s="72" t="s">
+      <c r="CV1" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="CT1" s="27" t="s">
+      <c r="CW1" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="CU1" s="28" t="s">
+      <c r="CX1" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="CV1" s="72" t="s">
+      <c r="CY1" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="CW1" s="27" t="s">
+      <c r="CZ1" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="CX1" s="28" t="s">
+      <c r="DA1" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="CY1" s="72" t="s">
+      <c r="DB1" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="CZ1" s="27" t="s">
+      <c r="DC1" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="DA1" s="28" t="s">
+      <c r="DD1" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="DB1" s="72" t="s">
+      <c r="DE1" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="DC1" s="29" t="s">
+      <c r="DF1" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="DG1" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="DH1" s="67" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI1" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="DJ1" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="DK1" s="67" t="s">
+        <v>214</v>
+      </c>
+      <c r="DL1" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="DM1" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="DN1" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="DO1" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="DP1" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="DQ1" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="DR1" s="29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>208</v>
       </c>
@@ -1762,161 +1850,195 @@
       </c>
       <c r="AL2" s="32"/>
       <c r="AM2" s="35"/>
-      <c r="AN2" s="69" t="str">
+      <c r="AN2" s="64" t="str">
         <f t="shared" ref="AN2:AN13" si="1">IF(AL2=0,"NA",AM2-$AD2)</f>
         <v>NA</v>
       </c>
       <c r="AO2" s="32">
         <v>1</v>
       </c>
-      <c r="AP2" s="69">
+      <c r="AP2" s="64">
         <v>1.7106481481481483E-2</v>
       </c>
       <c r="AQ2" s="34">
         <f t="shared" ref="AQ2:AQ13" si="2">IF(AO2=0,"NA",AP2-$AD2)</f>
         <v>1.3298611111111112E-2</v>
       </c>
-      <c r="AR2" s="71"/>
-      <c r="AS2" s="70"/>
+      <c r="AR2" s="66"/>
+      <c r="AS2" s="65"/>
       <c r="AT2" s="34" t="str">
         <f t="shared" ref="AT2:AT13" si="3">IF(AR2=0,"NA",AS2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="AU2" s="71"/>
-      <c r="AV2" s="70"/>
+      <c r="AU2" s="66"/>
+      <c r="AV2" s="65"/>
       <c r="AW2" s="34" t="str">
         <f t="shared" ref="AW2:AW13" si="4">IF(AU2=0,"NA",AV2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="AX2" s="71"/>
-      <c r="AY2" s="70"/>
+      <c r="AX2" s="66"/>
+      <c r="AY2" s="65"/>
       <c r="AZ2" s="34" t="str">
         <f t="shared" ref="AZ2:AZ22" si="5">IF(AX2=0,"NA",AY2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BA2" s="71"/>
-      <c r="BB2" s="70"/>
+      <c r="BA2" s="66"/>
+      <c r="BB2" s="65"/>
       <c r="BC2" s="34" t="str">
         <f t="shared" ref="BC2:BC13" si="6">IF(BA2=0,"NA",BB2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BD2" s="71"/>
-      <c r="BE2" s="70"/>
+      <c r="BD2" s="66"/>
+      <c r="BE2" s="65"/>
       <c r="BF2" s="34" t="str">
         <f t="shared" ref="BF2:BF13" si="7">IF(BD2=0,"NA",BE2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BG2" s="71"/>
-      <c r="BH2" s="70"/>
+      <c r="BG2" s="66"/>
+      <c r="BH2" s="65"/>
       <c r="BI2" s="34" t="str">
         <f t="shared" ref="BI2:BI13" si="8">IF(BG2=0,"NA",BH2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BJ2" s="71"/>
-      <c r="BK2" s="70"/>
+      <c r="BJ2" s="66"/>
+      <c r="BK2" s="65"/>
       <c r="BL2" s="34" t="str">
         <f t="shared" ref="BL2:BL13" si="9">IF(BJ2=0,"NA",BK2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BM2" s="71"/>
-      <c r="BN2" s="70"/>
+      <c r="BM2" s="66"/>
+      <c r="BN2" s="65"/>
       <c r="BO2" s="34" t="str">
         <f t="shared" ref="BO2:BO13" si="10">IF(BM2=0,"NA",BN2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BP2" s="71"/>
-      <c r="BQ2" s="70"/>
+      <c r="BP2" s="66"/>
+      <c r="BQ2" s="65"/>
       <c r="BR2" s="34" t="str">
         <f t="shared" ref="BR2:BR13" si="11">IF(BP2=0,"NA",BQ2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BS2" s="71">
+      <c r="BS2" s="66">
         <v>1</v>
       </c>
-      <c r="BT2" s="89">
+      <c r="BT2" s="80">
         <v>1.2037037037037035E-2</v>
       </c>
       <c r="BU2" s="34">
         <f t="shared" ref="BU2:BU13" si="12">IF(BS2=0,"NA",BT2-$AD2)</f>
         <v>8.2291666666666641E-3</v>
       </c>
-      <c r="BV2" s="71"/>
-      <c r="BW2" s="70"/>
+      <c r="BV2" s="66"/>
+      <c r="BW2" s="65"/>
       <c r="BX2" s="34" t="str">
         <f t="shared" ref="BX2:BX22" si="13">IF(BV2=0,"NA",BW2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BY2" s="86"/>
-      <c r="BZ2" s="69"/>
+      <c r="BY2" s="33"/>
+      <c r="BZ2" s="64"/>
       <c r="CA2" s="34" t="str">
         <f t="shared" ref="CA2:CA22" si="14">IF(BY2=0,"NA",BZ2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CB2" s="71">
+      <c r="CB2" s="66">
         <v>1</v>
       </c>
-      <c r="CC2" s="84">
+      <c r="CC2" s="79">
         <v>1.8553240740740742E-2</v>
       </c>
       <c r="CD2" s="34">
         <f t="shared" ref="CD2:CD22" si="15">IF(CB2=0,"NA",CC2-$AD2)</f>
         <v>1.474537037037037E-2</v>
       </c>
-      <c r="CE2" s="71"/>
-      <c r="CF2" s="84"/>
+      <c r="CE2" s="66"/>
+      <c r="CF2" s="79"/>
       <c r="CG2" s="34" t="str">
         <f t="shared" ref="CG2:CG22" si="16">IF(CE2=0,"NA",CF2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CH2" s="71"/>
-      <c r="CI2" s="84"/>
+      <c r="CH2" s="66"/>
+      <c r="CI2" s="79"/>
       <c r="CJ2" s="34" t="str">
         <f t="shared" ref="CJ2:CJ22" si="17">IF(CH2=0,"NA",CI2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CK2" s="71"/>
-      <c r="CL2" s="84"/>
+      <c r="CK2" s="66"/>
+      <c r="CL2" s="79"/>
       <c r="CM2" s="34" t="str">
         <f t="shared" ref="CM2:CM22" si="18">IF(CK2=0,"NA",CL2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CN2" s="71"/>
-      <c r="CO2" s="84"/>
+      <c r="CN2" s="66"/>
+      <c r="CO2" s="79"/>
       <c r="CP2" s="34" t="str">
         <f t="shared" ref="CP2:CP22" si="19">IF(CN2=0,"NA",CO2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CQ2" s="71"/>
-      <c r="CR2" s="84"/>
+      <c r="CQ2" s="66"/>
+      <c r="CR2" s="79"/>
       <c r="CS2" s="34" t="str">
         <f t="shared" ref="CS2:CS22" si="20">IF(CQ2=0,"NA",CR2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CT2" s="71"/>
-      <c r="CU2" s="84"/>
+      <c r="CT2" s="66"/>
+      <c r="CU2" s="79"/>
       <c r="CV2" s="34" t="str">
         <f t="shared" ref="CV2:CV22" si="21">IF(CT2=0,"NA",CU2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CW2" s="71"/>
-      <c r="CX2" s="84"/>
+      <c r="CW2" s="66"/>
+      <c r="CX2" s="79"/>
       <c r="CY2" s="34" t="str">
         <f t="shared" ref="CY2:CY22" si="22">IF(CW2=0,"NA",CX2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CZ2" s="71">
+      <c r="CZ2" s="66"/>
+      <c r="DA2" s="79"/>
+      <c r="DB2" s="34" t="str">
+        <f t="shared" ref="DB2:DB22" si="23">IF(CZ2=0,"NA",DA2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DC2" s="66">
         <v>3</v>
       </c>
-      <c r="DA2" s="84">
+      <c r="DD2" s="79">
         <v>4.1319444444444442E-3</v>
       </c>
-      <c r="DB2" s="34">
-        <f t="shared" ref="DB2:DB13" si="23">IF(CZ2=0,"NA",DA2-$AD2)</f>
+      <c r="DE2" s="34">
+        <f t="shared" ref="DE2:DE22" si="24">IF(DC2=0,"NA",DD2-$AD2)</f>
         <v>3.2407407407407341E-4</v>
       </c>
-      <c r="DC2" s="37"/>
+      <c r="DF2" s="66">
+        <v>1</v>
+      </c>
+      <c r="DG2" s="79">
+        <v>2.2488425925925926E-2</v>
+      </c>
+      <c r="DH2" s="34">
+        <f t="shared" ref="DH2:DH22" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
+        <v>1.8680555555555554E-2</v>
+      </c>
+      <c r="DI2" s="66"/>
+      <c r="DJ2" s="79"/>
+      <c r="DK2" s="34" t="str">
+        <f t="shared" ref="DK2:DK22" si="26">IF(DI2=0,"NA",DJ2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DL2" s="66"/>
+      <c r="DM2" s="79"/>
+      <c r="DN2" s="34" t="str">
+        <f t="shared" ref="DN2:DN22" si="27">IF(DL2=0,"NA",DM2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DO2" s="66"/>
+      <c r="DP2" s="79"/>
+      <c r="DQ2" s="34" t="str">
+        <f t="shared" ref="DQ2:DQ13" si="28">IF(DO2=0,"NA",DP2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DR2" s="37"/>
     </row>
-    <row r="3" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>208</v>
       </c>
@@ -1933,7 +2055,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="5" t="str">
-        <f t="shared" ref="F3:F22" si="24">D3&amp;""&amp;E3</f>
+        <f t="shared" ref="F3:F22" si="29">D3&amp;""&amp;E3</f>
         <v>D3</v>
       </c>
       <c r="G3" s="5">
@@ -2001,7 +2123,7 @@
         <v>1.1342592592592591E-3</v>
       </c>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC22" si="25">SUM(W3:AB3)</f>
+        <f t="shared" ref="AC3:AC22" si="30">SUM(W3:AB3)</f>
         <v>7.8148148148148147E-2</v>
       </c>
       <c r="AD3" s="20">
@@ -2029,7 +2151,7 @@
       </c>
       <c r="AL3" s="32"/>
       <c r="AM3" s="35"/>
-      <c r="AN3" s="69" t="str">
+      <c r="AN3" s="64" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
@@ -2105,8 +2227,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY3" s="86"/>
-      <c r="BZ3" s="69"/>
+      <c r="BY3" s="33"/>
+      <c r="BZ3" s="64"/>
       <c r="CA3" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -2165,9 +2287,39 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC3" s="37"/>
+      <c r="DC3" s="32"/>
+      <c r="DD3" s="33"/>
+      <c r="DE3" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF3" s="32"/>
+      <c r="DG3" s="33"/>
+      <c r="DH3" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI3" s="32"/>
+      <c r="DJ3" s="33"/>
+      <c r="DK3" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL3" s="32"/>
+      <c r="DM3" s="33"/>
+      <c r="DN3" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO3" s="32"/>
+      <c r="DP3" s="33"/>
+      <c r="DQ3" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR3" s="37"/>
     </row>
-    <row r="4" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>208</v>
       </c>
@@ -2184,7 +2336,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>L2</v>
       </c>
       <c r="G4" s="5">
@@ -2246,7 +2398,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>6.0902777777777778E-2</v>
       </c>
       <c r="AD4" s="20">
@@ -2278,15 +2430,19 @@
       <c r="AM4" s="35">
         <v>3.4236111111111113E-2</v>
       </c>
-      <c r="AN4" s="69">
+      <c r="AN4" s="64">
         <f t="shared" si="1"/>
         <v>3.0578703703703705E-2</v>
       </c>
-      <c r="AO4" s="32"/>
-      <c r="AP4" s="33"/>
-      <c r="AQ4" s="34" t="str">
+      <c r="AO4" s="32">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="35">
+        <v>2.8182870370370372E-2</v>
+      </c>
+      <c r="AQ4" s="34">
         <f t="shared" si="2"/>
-        <v>NA</v>
+        <v>2.4525462962962964E-2</v>
       </c>
       <c r="AR4" s="32"/>
       <c r="AS4" s="33"/>
@@ -2362,8 +2518,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY4" s="86"/>
-      <c r="BZ4" s="69"/>
+      <c r="BY4" s="33"/>
+      <c r="BZ4" s="64"/>
       <c r="CA4" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -2416,19 +2572,53 @@
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ4" s="32">
+      <c r="CZ4" s="32"/>
+      <c r="DA4" s="35"/>
+      <c r="DB4" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC4" s="32">
         <v>6</v>
       </c>
-      <c r="DA4" s="35">
+      <c r="DD4" s="35">
         <v>3.7731481481481483E-3</v>
       </c>
-      <c r="DB4" s="34">
-        <f t="shared" si="23"/>
+      <c r="DE4" s="34">
+        <f t="shared" si="24"/>
         <v>1.1574074074074091E-4</v>
       </c>
-      <c r="DC4" s="37"/>
+      <c r="DF4" s="32">
+        <v>1</v>
+      </c>
+      <c r="DG4" s="35">
+        <v>1.2060185185185186E-2</v>
+      </c>
+      <c r="DH4" s="34">
+        <f t="shared" si="25"/>
+        <v>8.4027777777777781E-3</v>
+      </c>
+      <c r="DI4" s="32"/>
+      <c r="DJ4" s="35"/>
+      <c r="DK4" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL4" s="32"/>
+      <c r="DM4" s="35"/>
+      <c r="DN4" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO4" s="32"/>
+      <c r="DP4" s="35"/>
+      <c r="DQ4" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR4" s="37"/>
     </row>
-    <row r="5" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>208</v>
       </c>
@@ -2445,7 +2635,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>L1</v>
       </c>
       <c r="G5" s="5">
@@ -2503,7 +2693,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD5" s="20"/>
@@ -2519,7 +2709,7 @@
       <c r="AK5" s="31"/>
       <c r="AL5" s="32"/>
       <c r="AM5" s="35"/>
-      <c r="AN5" s="69" t="str">
+      <c r="AN5" s="64" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
@@ -2595,8 +2785,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY5" s="86"/>
-      <c r="BZ5" s="69"/>
+      <c r="BY5" s="33"/>
+      <c r="BZ5" s="64"/>
       <c r="CA5" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -2655,9 +2845,39 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC5" s="37"/>
+      <c r="DC5" s="32"/>
+      <c r="DD5" s="33"/>
+      <c r="DE5" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF5" s="32"/>
+      <c r="DG5" s="33"/>
+      <c r="DH5" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI5" s="32"/>
+      <c r="DJ5" s="33"/>
+      <c r="DK5" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL5" s="32"/>
+      <c r="DM5" s="33"/>
+      <c r="DN5" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO5" s="32"/>
+      <c r="DP5" s="33"/>
+      <c r="DQ5" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR5" s="37"/>
     </row>
-    <row r="6" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>208</v>
       </c>
@@ -2674,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>D1</v>
       </c>
       <c r="G6" s="5">
@@ -2732,7 +2952,7 @@
       <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD6" s="20"/>
@@ -2748,7 +2968,7 @@
       <c r="AK6" s="31"/>
       <c r="AL6" s="32"/>
       <c r="AM6" s="35"/>
-      <c r="AN6" s="69" t="str">
+      <c r="AN6" s="64" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
@@ -2824,8 +3044,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY6" s="86"/>
-      <c r="BZ6" s="69"/>
+      <c r="BY6" s="33"/>
+      <c r="BZ6" s="64"/>
       <c r="CA6" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -2884,9 +3104,39 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC6" s="37"/>
+      <c r="DC6" s="32"/>
+      <c r="DD6" s="33"/>
+      <c r="DE6" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF6" s="32"/>
+      <c r="DG6" s="33"/>
+      <c r="DH6" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI6" s="32"/>
+      <c r="DJ6" s="33"/>
+      <c r="DK6" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL6" s="32"/>
+      <c r="DM6" s="33"/>
+      <c r="DN6" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO6" s="32"/>
+      <c r="DP6" s="33"/>
+      <c r="DQ6" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR6" s="37"/>
     </row>
-    <row r="7" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>208</v>
       </c>
@@ -2903,7 +3153,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>L3</v>
       </c>
       <c r="G7" s="5">
@@ -2961,7 +3211,7 @@
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD7" s="20"/>
@@ -2977,7 +3227,7 @@
       <c r="AK7" s="31"/>
       <c r="AL7" s="32"/>
       <c r="AM7" s="35"/>
-      <c r="AN7" s="69" t="str">
+      <c r="AN7" s="64" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
@@ -3053,8 +3303,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY7" s="86"/>
-      <c r="BZ7" s="69"/>
+      <c r="BY7" s="33"/>
+      <c r="BZ7" s="64"/>
       <c r="CA7" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -3113,9 +3363,39 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC7" s="37"/>
+      <c r="DC7" s="32"/>
+      <c r="DD7" s="33"/>
+      <c r="DE7" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF7" s="32"/>
+      <c r="DG7" s="33"/>
+      <c r="DH7" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI7" s="32"/>
+      <c r="DJ7" s="33"/>
+      <c r="DK7" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL7" s="32"/>
+      <c r="DM7" s="33"/>
+      <c r="DN7" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO7" s="32"/>
+      <c r="DP7" s="33"/>
+      <c r="DQ7" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR7" s="37"/>
     </row>
-    <row r="8" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>208</v>
       </c>
@@ -3132,7 +3412,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>L3</v>
       </c>
       <c r="G8" s="5">
@@ -3194,7 +3474,7 @@
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>5.3020833333333336E-2</v>
       </c>
       <c r="AD8" s="20">
@@ -3222,14 +3502,14 @@
       </c>
       <c r="AL8" s="32"/>
       <c r="AM8" s="35"/>
-      <c r="AN8" s="69" t="str">
+      <c r="AN8" s="64" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
       <c r="AO8" s="32">
         <v>3</v>
       </c>
-      <c r="AP8" s="83">
+      <c r="AP8" s="78">
         <v>0.28819444444444448</v>
       </c>
       <c r="AQ8" s="34">
@@ -3302,8 +3582,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY8" s="86"/>
-      <c r="BZ8" s="69"/>
+      <c r="BY8" s="33"/>
+      <c r="BZ8" s="64"/>
       <c r="CA8" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -3345,30 +3625,64 @@
         <v>NA</v>
       </c>
       <c r="CT8" s="32"/>
-      <c r="CU8" s="83"/>
+      <c r="CU8" s="33"/>
       <c r="CV8" s="34" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW8" s="32"/>
-      <c r="CX8" s="83"/>
+      <c r="CX8" s="78"/>
       <c r="CY8" s="34" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ8" s="32">
+      <c r="CZ8" s="32"/>
+      <c r="DA8" s="78"/>
+      <c r="DB8" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC8" s="32">
         <v>5</v>
       </c>
-      <c r="DA8" s="83">
+      <c r="DD8" s="78">
         <v>0.25694444444444448</v>
       </c>
-      <c r="DB8" s="34">
-        <f t="shared" si="23"/>
+      <c r="DE8" s="34">
+        <f t="shared" si="24"/>
         <v>0.25300925925925927</v>
       </c>
-      <c r="DC8" s="37"/>
+      <c r="DF8" s="32"/>
+      <c r="DG8" s="78"/>
+      <c r="DH8" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI8" s="32"/>
+      <c r="DJ8" s="78"/>
+      <c r="DK8" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL8" s="32">
+        <v>1</v>
+      </c>
+      <c r="DM8" s="78">
+        <v>2.3831018518518519E-2</v>
+      </c>
+      <c r="DN8" s="34">
+        <f t="shared" si="27"/>
+        <v>1.9895833333333335E-2</v>
+      </c>
+      <c r="DO8" s="32"/>
+      <c r="DP8" s="78"/>
+      <c r="DQ8" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR8" s="37"/>
     </row>
-    <row r="9" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>208</v>
       </c>
@@ -3385,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>D1</v>
       </c>
       <c r="G9" s="5">
@@ -3449,7 +3763,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>4.5902777777777778E-2</v>
       </c>
       <c r="AD9" s="20">
@@ -3479,7 +3793,7 @@
       <c r="AM9" s="35">
         <v>2.5358796296296296E-2</v>
       </c>
-      <c r="AN9" s="69">
+      <c r="AN9" s="64">
         <f t="shared" si="1"/>
         <v>2.1574074074074072E-2</v>
       </c>
@@ -3559,8 +3873,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY9" s="86"/>
-      <c r="BZ9" s="69"/>
+      <c r="BY9" s="33"/>
+      <c r="BZ9" s="64"/>
       <c r="CA9" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -3602,30 +3916,60 @@
         <v>NA</v>
       </c>
       <c r="CT9" s="32"/>
-      <c r="CU9" s="69"/>
+      <c r="CU9" s="33"/>
       <c r="CV9" s="34" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW9" s="32"/>
-      <c r="CX9" s="69"/>
+      <c r="CX9" s="64"/>
       <c r="CY9" s="34" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ9" s="32">
+      <c r="CZ9" s="32"/>
+      <c r="DA9" s="64"/>
+      <c r="DB9" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC9" s="32">
         <v>2</v>
       </c>
-      <c r="DA9" s="69">
+      <c r="DD9" s="64">
         <v>2.193287037037037E-2</v>
       </c>
-      <c r="DB9" s="34">
-        <f t="shared" si="23"/>
+      <c r="DE9" s="34">
+        <f t="shared" si="24"/>
         <v>1.8148148148148149E-2</v>
       </c>
-      <c r="DC9" s="37"/>
+      <c r="DF9" s="32"/>
+      <c r="DG9" s="64"/>
+      <c r="DH9" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI9" s="32"/>
+      <c r="DJ9" s="64"/>
+      <c r="DK9" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL9" s="32"/>
+      <c r="DM9" s="64"/>
+      <c r="DN9" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO9" s="32"/>
+      <c r="DP9" s="64"/>
+      <c r="DQ9" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR9" s="37"/>
     </row>
-    <row r="10" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>208</v>
       </c>
@@ -3642,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>L1</v>
       </c>
       <c r="G10" s="5">
@@ -3710,7 +4054,7 @@
       </c>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>5.2268518518518513E-2</v>
       </c>
       <c r="AD10" s="20">
@@ -3742,7 +4086,7 @@
       <c r="AM10" s="35">
         <v>1.8634259259259257E-2</v>
       </c>
-      <c r="AN10" s="69">
+      <c r="AN10" s="64">
         <f t="shared" si="1"/>
         <v>1.3993055555555554E-2</v>
       </c>
@@ -3822,8 +4166,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY10" s="86"/>
-      <c r="BZ10" s="69"/>
+      <c r="BY10" s="33"/>
+      <c r="BZ10" s="64"/>
       <c r="CA10" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -3876,19 +4220,49 @@
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ10" s="32">
+      <c r="CZ10" s="32"/>
+      <c r="DA10" s="35"/>
+      <c r="DB10" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC10" s="32">
         <v>2</v>
       </c>
-      <c r="DA10" s="35">
+      <c r="DD10" s="35">
         <v>6.8402777777777776E-3</v>
       </c>
-      <c r="DB10" s="34">
-        <f t="shared" si="23"/>
+      <c r="DE10" s="34">
+        <f t="shared" si="24"/>
         <v>2.1990740740740738E-3</v>
       </c>
-      <c r="DC10" s="37"/>
+      <c r="DF10" s="32"/>
+      <c r="DG10" s="35"/>
+      <c r="DH10" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI10" s="32"/>
+      <c r="DJ10" s="35"/>
+      <c r="DK10" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL10" s="32"/>
+      <c r="DM10" s="35"/>
+      <c r="DN10" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO10" s="32"/>
+      <c r="DP10" s="35"/>
+      <c r="DQ10" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR10" s="37"/>
     </row>
-    <row r="11" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>208</v>
       </c>
@@ -3905,7 +4279,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>E2</v>
       </c>
       <c r="G11" s="5">
@@ -3965,7 +4339,7 @@
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>5.1307870370370365E-2</v>
       </c>
       <c r="AD11" s="20">
@@ -3997,7 +4371,7 @@
       <c r="AM11" s="35">
         <v>2.3645833333333335E-2</v>
       </c>
-      <c r="AN11" s="69">
+      <c r="AN11" s="64">
         <f t="shared" si="1"/>
         <v>2.0104166666666669E-2</v>
       </c>
@@ -4023,15 +4397,11 @@
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AX11" s="32">
-        <v>14</v>
-      </c>
-      <c r="AY11" s="35">
-        <v>4.2939814814814811E-3</v>
-      </c>
-      <c r="AZ11" s="34">
+      <c r="AX11" s="32"/>
+      <c r="AY11" s="35"/>
+      <c r="AZ11" s="34" t="str">
         <f t="shared" si="5"/>
-        <v>7.523148148148146E-4</v>
+        <v>NA</v>
       </c>
       <c r="BA11" s="32">
         <v>1</v>
@@ -4059,11 +4429,15 @@
         <f t="shared" si="8"/>
         <v>2.0104166666666669E-2</v>
       </c>
-      <c r="BJ11" s="32"/>
-      <c r="BK11" s="33"/>
-      <c r="BL11" s="34" t="str">
+      <c r="BJ11" s="32">
+        <v>14</v>
+      </c>
+      <c r="BK11" s="35">
+        <v>4.2939814814814811E-3</v>
+      </c>
+      <c r="BL11" s="34">
         <f t="shared" si="9"/>
-        <v>NA</v>
+        <v>7.523148148148146E-4</v>
       </c>
       <c r="BM11" s="32">
         <v>1</v>
@@ -4093,10 +4467,10 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY11" s="86">
+      <c r="BY11" s="33">
         <v>1</v>
       </c>
-      <c r="BZ11" s="69">
+      <c r="BZ11" s="64">
         <v>2.929398148148148E-2</v>
       </c>
       <c r="CA11" s="34">
@@ -4110,36 +4484,40 @@
         <v>NA</v>
       </c>
       <c r="CE11" s="32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CF11" s="35">
-        <v>4.5173611111111116E-2</v>
+        <v>3.2754629629629627E-2</v>
       </c>
       <c r="CG11" s="34">
         <f t="shared" si="16"/>
+        <v>2.9212962962962961E-2</v>
+      </c>
+      <c r="CH11" s="32">
+        <v>1</v>
+      </c>
+      <c r="CI11" s="35">
+        <v>4.5173611111111116E-2</v>
+      </c>
+      <c r="CJ11" s="34">
+        <f t="shared" si="17"/>
         <v>4.1631944444444451E-2</v>
       </c>
-      <c r="CH11" s="32"/>
-      <c r="CI11" s="35"/>
-      <c r="CJ11" s="34" t="str">
-        <f t="shared" si="17"/>
-        <v>NA</v>
-      </c>
-      <c r="CK11" s="32">
+      <c r="CK11" s="32"/>
+      <c r="CL11" s="35"/>
+      <c r="CM11" s="34" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CN11" s="32">
         <v>1</v>
       </c>
-      <c r="CL11" s="35">
+      <c r="CO11" s="35">
         <v>4.9178240740740738E-2</v>
       </c>
-      <c r="CM11" s="34">
-        <f t="shared" si="18"/>
+      <c r="CP11" s="34">
+        <f t="shared" si="19"/>
         <v>4.5636574074074072E-2</v>
-      </c>
-      <c r="CN11" s="32"/>
-      <c r="CO11" s="35"/>
-      <c r="CP11" s="34" t="str">
-        <f t="shared" si="19"/>
-        <v>NA</v>
       </c>
       <c r="CQ11" s="32"/>
       <c r="CR11" s="35"/>
@@ -4163,15 +4541,53 @@
         <v>1</v>
       </c>
       <c r="DA11" s="35">
-        <v>4.2245370370370371E-3</v>
+        <v>1.1944444444444445E-2</v>
       </c>
       <c r="DB11" s="34">
         <f t="shared" si="23"/>
+        <v>8.4027777777777781E-3</v>
+      </c>
+      <c r="DC11" s="32">
+        <v>1</v>
+      </c>
+      <c r="DD11" s="35">
+        <v>4.2245370370370371E-3</v>
+      </c>
+      <c r="DE11" s="34">
+        <f t="shared" si="24"/>
         <v>6.8287037037037058E-4</v>
       </c>
-      <c r="DC11" s="37"/>
+      <c r="DF11" s="32">
+        <v>1</v>
+      </c>
+      <c r="DG11" s="35">
+        <v>3.3969907407407407E-2</v>
+      </c>
+      <c r="DH11" s="34">
+        <f t="shared" si="25"/>
+        <v>3.0428240740740742E-2</v>
+      </c>
+      <c r="DI11" s="32"/>
+      <c r="DJ11" s="35"/>
+      <c r="DK11" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL11" s="32"/>
+      <c r="DM11" s="35"/>
+      <c r="DN11" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO11" s="32"/>
+      <c r="DP11" s="35"/>
+      <c r="DQ11" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR11" s="37"/>
     </row>
-    <row r="12" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>208</v>
       </c>
@@ -4188,7 +4604,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>E3</v>
       </c>
       <c r="G12" s="5">
@@ -4250,7 +4666,7 @@
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>4.9548611111111106E-2</v>
       </c>
       <c r="AD12" s="20">
@@ -4278,7 +4694,7 @@
       </c>
       <c r="AL12" s="32"/>
       <c r="AM12" s="35"/>
-      <c r="AN12" s="69" t="str">
+      <c r="AN12" s="64" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
@@ -4354,73 +4770,107 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY12" s="86"/>
-      <c r="BZ12" s="69"/>
+      <c r="BY12" s="33"/>
+      <c r="BZ12" s="64"/>
       <c r="CA12" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
       </c>
       <c r="CB12" s="32"/>
-      <c r="CC12" s="83"/>
+      <c r="CC12" s="78"/>
       <c r="CD12" s="34" t="str">
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE12" s="32"/>
-      <c r="CF12" s="83"/>
+      <c r="CF12" s="78"/>
       <c r="CG12" s="34" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CH12" s="32"/>
-      <c r="CI12" s="83"/>
+      <c r="CI12" s="78"/>
       <c r="CJ12" s="34" t="str">
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CK12" s="32"/>
-      <c r="CL12" s="83"/>
+      <c r="CL12" s="78"/>
       <c r="CM12" s="34" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CN12" s="32"/>
-      <c r="CO12" s="83"/>
+      <c r="CO12" s="78"/>
       <c r="CP12" s="34" t="str">
         <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CQ12" s="32"/>
-      <c r="CR12" s="83"/>
+      <c r="CR12" s="78"/>
       <c r="CS12" s="34" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT12" s="32"/>
-      <c r="CU12" s="83"/>
+      <c r="CU12" s="78"/>
       <c r="CV12" s="34" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW12" s="32"/>
-      <c r="CX12" s="83"/>
+      <c r="CX12" s="78"/>
       <c r="CY12" s="34" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ12" s="32">
+      <c r="CZ12" s="32"/>
+      <c r="DA12" s="78"/>
+      <c r="DB12" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC12" s="32">
         <v>5</v>
       </c>
-      <c r="DA12" s="83">
+      <c r="DD12" s="78">
         <v>1.2997685185185183E-2</v>
       </c>
-      <c r="DB12" s="34">
-        <f t="shared" si="23"/>
+      <c r="DE12" s="34">
+        <f t="shared" si="24"/>
         <v>9.2939814814814795E-3</v>
       </c>
-      <c r="DC12" s="37"/>
+      <c r="DF12" s="32"/>
+      <c r="DG12" s="78"/>
+      <c r="DH12" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI12" s="32">
+        <v>1</v>
+      </c>
+      <c r="DJ12" s="78">
+        <v>6.7939814814814816E-3</v>
+      </c>
+      <c r="DK12" s="34">
+        <f t="shared" si="26"/>
+        <v>3.0902777777777782E-3</v>
+      </c>
+      <c r="DL12" s="32"/>
+      <c r="DM12" s="78"/>
+      <c r="DN12" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO12" s="32"/>
+      <c r="DP12" s="78"/>
+      <c r="DQ12" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR12" s="37"/>
     </row>
-    <row r="13" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>208</v>
       </c>
@@ -4437,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>E1</v>
       </c>
       <c r="G13" s="5">
@@ -4497,7 +4947,7 @@
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>5.5509259259259258E-2</v>
       </c>
       <c r="AD13" s="20">
@@ -4529,7 +4979,7 @@
       <c r="AM13" s="35">
         <v>2.6550925925925926E-2</v>
       </c>
-      <c r="AN13" s="69">
+      <c r="AN13" s="64">
         <f t="shared" si="1"/>
         <v>2.2141203703703705E-2</v>
       </c>
@@ -4613,8 +5063,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY13" s="86"/>
-      <c r="BZ13" s="69"/>
+      <c r="BY13" s="33"/>
+      <c r="BZ13" s="64"/>
       <c r="CA13" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -4643,31 +5093,31 @@
         <f t="shared" si="18"/>
         <v>NA</v>
       </c>
-      <c r="CN13" s="32">
+      <c r="CN13" s="32"/>
+      <c r="CO13" s="33"/>
+      <c r="CP13" s="34" t="str">
+        <f t="shared" si="19"/>
+        <v>NA</v>
+      </c>
+      <c r="CQ13" s="32">
         <v>1</v>
       </c>
-      <c r="CO13" s="35">
+      <c r="CR13" s="35">
         <v>2.326388888888889E-2</v>
-      </c>
-      <c r="CP13" s="34">
-        <f t="shared" si="19"/>
-        <v>1.8854166666666668E-2</v>
-      </c>
-      <c r="CQ13" s="32">
-        <v>2</v>
-      </c>
-      <c r="CR13" s="35">
-        <v>3.3321759259259259E-2</v>
       </c>
       <c r="CS13" s="34">
         <f t="shared" si="20"/>
+        <v>1.8854166666666668E-2</v>
+      </c>
+      <c r="CT13" s="32">
+        <v>2</v>
+      </c>
+      <c r="CU13" s="35">
+        <v>3.3321759259259259E-2</v>
+      </c>
+      <c r="CV13" s="34">
+        <f t="shared" si="21"/>
         <v>2.8912037037037038E-2</v>
-      </c>
-      <c r="CT13" s="32"/>
-      <c r="CU13" s="33"/>
-      <c r="CV13" s="34" t="str">
-        <f t="shared" si="21"/>
-        <v>NA</v>
       </c>
       <c r="CW13" s="32"/>
       <c r="CX13" s="33"/>
@@ -4681,9 +5131,43 @@
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC13" s="37"/>
+      <c r="DC13" s="32"/>
+      <c r="DD13" s="33"/>
+      <c r="DE13" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF13" s="32">
+        <v>1</v>
+      </c>
+      <c r="DG13" s="35">
+        <v>2.1180555555555557E-2</v>
+      </c>
+      <c r="DH13" s="34">
+        <f t="shared" si="25"/>
+        <v>1.6770833333333336E-2</v>
+      </c>
+      <c r="DI13" s="32"/>
+      <c r="DJ13" s="33"/>
+      <c r="DK13" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL13" s="32"/>
+      <c r="DM13" s="33"/>
+      <c r="DN13" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO13" s="32"/>
+      <c r="DP13" s="33"/>
+      <c r="DQ13" s="34" t="str">
+        <f t="shared" si="28"/>
+        <v>NA</v>
+      </c>
+      <c r="DR13" s="37"/>
     </row>
-    <row r="14" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>208</v>
       </c>
@@ -4700,7 +5184,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>E4</v>
       </c>
       <c r="G14" s="5">
@@ -4764,7 +5248,7 @@
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>6.1759259259259257E-2</v>
       </c>
       <c r="AD14" s="20">
@@ -4774,7 +5258,7 @@
         <v>1.5127314814814816E-2</v>
       </c>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF22" si="26">AC14-AD14-AE14</f>
+        <f t="shared" ref="AF14:AF22" si="31">AC14-AD14-AE14</f>
         <v>4.2905092592592592E-2</v>
       </c>
       <c r="AG14" s="21">
@@ -4793,25 +5277,25 @@
       <c r="AL14" s="32"/>
       <c r="AM14" s="33"/>
       <c r="AN14" s="34" t="str">
-        <f t="shared" ref="AN14:AN22" si="27">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN22" si="32">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AO14" s="32"/>
       <c r="AP14" s="33"/>
       <c r="AQ14" s="34" t="str">
-        <f t="shared" ref="AQ14:AQ22" si="28">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ22" si="33">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AR14" s="32"/>
       <c r="AS14" s="33"/>
       <c r="AT14" s="34" t="str">
-        <f t="shared" ref="AT14:AT22" si="29">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT22" si="34">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AU14" s="33"/>
       <c r="AV14" s="33"/>
       <c r="AW14" s="34" t="str">
-        <f t="shared" ref="AW14:AW22" si="30">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW22" si="35">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="32"/>
@@ -4823,19 +5307,19 @@
       <c r="BA14" s="32"/>
       <c r="BB14" s="35"/>
       <c r="BC14" s="34" t="str">
-        <f t="shared" ref="BC14:BC22" si="31">IF(BA14=0,"NA",BB14-$AD14)</f>
+        <f t="shared" ref="BC14:BC22" si="36">IF(BA14=0,"NA",BB14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BD14" s="32"/>
       <c r="BE14" s="33"/>
       <c r="BF14" s="34" t="str">
-        <f t="shared" ref="BF14:BF22" si="32">IF(BD14=0,"NA",BE14-$AD14)</f>
+        <f t="shared" ref="BF14:BF22" si="37">IF(BD14=0,"NA",BE14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BG14" s="32"/>
       <c r="BH14" s="35"/>
       <c r="BI14" s="34" t="str">
-        <f t="shared" ref="BI14:BI22" si="33">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI22" si="38">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="32">
@@ -4845,19 +5329,19 @@
         <v>1.8148148148148146E-2</v>
       </c>
       <c r="BL14" s="34">
-        <f t="shared" ref="BL14:BL22" si="34">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <f t="shared" ref="BL14:BL22" si="39">IF(BJ14=0,"NA",BK14-$AD14)</f>
         <v>1.4421296296296295E-2</v>
       </c>
       <c r="BM14" s="33"/>
       <c r="BN14" s="33"/>
       <c r="BO14" s="34" t="str">
-        <f t="shared" ref="BO14:BO22" si="35">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <f t="shared" ref="BO14:BO22" si="40">IF(BM14=0,"NA",BN14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BP14" s="32"/>
       <c r="BQ14" s="33"/>
       <c r="BR14" s="34" t="str">
-        <f t="shared" ref="BR14:BR22" si="36">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR22" si="41">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="32">
@@ -4867,7 +5351,7 @@
         <v>1.653935185185185E-2</v>
       </c>
       <c r="BU14" s="34">
-        <f t="shared" ref="BU14:BU22" si="37">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <f t="shared" ref="BU14:BU22" si="42">IF(BS14=0,"NA",BT14-$AD14)</f>
         <v>1.2812499999999999E-2</v>
       </c>
       <c r="BV14" s="32"/>
@@ -4876,8 +5360,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY14" s="86"/>
-      <c r="BZ14" s="69"/>
+      <c r="BY14" s="33"/>
+      <c r="BZ14" s="64"/>
       <c r="CA14" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -4933,12 +5417,54 @@
       <c r="CZ14" s="32"/>
       <c r="DA14" s="33"/>
       <c r="DB14" s="34" t="str">
-        <f t="shared" ref="DB14:DB22" si="38">IF(CZ14=0,"NA",DA14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="DC14" s="37"/>
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC14" s="32"/>
+      <c r="DD14" s="33"/>
+      <c r="DE14" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF14" s="32">
+        <v>1</v>
+      </c>
+      <c r="DG14" s="35">
+        <v>6.1342592592592594E-3</v>
+      </c>
+      <c r="DH14" s="34">
+        <f t="shared" si="25"/>
+        <v>2.407407407407408E-3</v>
+      </c>
+      <c r="DI14" s="32">
+        <v>1</v>
+      </c>
+      <c r="DJ14" s="35">
+        <v>2.0023148148148148E-2</v>
+      </c>
+      <c r="DK14" s="34">
+        <f t="shared" si="26"/>
+        <v>1.6296296296296295E-2</v>
+      </c>
+      <c r="DL14" s="32">
+        <v>1</v>
+      </c>
+      <c r="DM14" s="35">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="DN14" s="34">
+        <f t="shared" si="27"/>
+        <v>1.2939814814814815E-2</v>
+      </c>
+      <c r="DO14" s="32"/>
+      <c r="DP14" s="35"/>
+      <c r="DQ14" s="34" t="str">
+        <f t="shared" ref="DQ14:DQ22" si="43">IF(DO14=0,"NA",DP14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="DR14" s="37"/>
     </row>
-    <row r="15" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>208</v>
       </c>
@@ -4955,7 +5481,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>E6</v>
       </c>
       <c r="G15" s="5">
@@ -5017,7 +5543,7 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>5.0416666666666665E-2</v>
       </c>
       <c r="AD15" s="20">
@@ -5025,7 +5551,7 @@
       </c>
       <c r="AE15" s="20"/>
       <c r="AF15" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>4.4537037037037035E-2</v>
       </c>
       <c r="AG15" s="21">
@@ -5036,10 +5562,10 @@
       </c>
       <c r="AI15" s="22"/>
       <c r="AJ15" s="30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK15" s="31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL15" s="32">
         <v>2</v>
@@ -5048,25 +5574,25 @@
         <v>1.3333333333333334E-2</v>
       </c>
       <c r="AN15" s="34">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>7.4537037037037046E-3</v>
       </c>
       <c r="AO15" s="32"/>
       <c r="AP15" s="33"/>
       <c r="AQ15" s="34" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AR15" s="32"/>
       <c r="AS15" s="33"/>
       <c r="AT15" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AU15" s="33"/>
       <c r="AV15" s="33"/>
       <c r="AW15" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="32"/>
@@ -5078,37 +5604,37 @@
       <c r="BA15" s="32"/>
       <c r="BB15" s="33"/>
       <c r="BC15" s="34" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="BD15" s="32"/>
       <c r="BE15" s="33"/>
       <c r="BF15" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG15" s="32"/>
       <c r="BH15" s="35"/>
       <c r="BI15" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="32"/>
       <c r="BK15" s="33"/>
       <c r="BL15" s="34" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BM15" s="32"/>
       <c r="BN15" s="33"/>
       <c r="BO15" s="34" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP15" s="32"/>
       <c r="BQ15" s="33"/>
       <c r="BR15" s="34" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS15" s="32">
@@ -5118,23 +5644,23 @@
         <v>7.9976851851851858E-3</v>
       </c>
       <c r="BU15" s="34">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>2.1180555555555562E-3</v>
       </c>
       <c r="BV15" s="32">
         <v>1</v>
       </c>
-      <c r="BW15" s="83">
+      <c r="BW15" s="78">
         <v>1.2731481481481481E-2</v>
       </c>
       <c r="BX15" s="34">
         <f t="shared" si="13"/>
         <v>6.8518518518518512E-3</v>
       </c>
-      <c r="BY15" s="86">
+      <c r="BY15" s="33">
         <v>1</v>
       </c>
-      <c r="BZ15" s="69">
+      <c r="BZ15" s="64">
         <v>1.0034722222222221E-2</v>
       </c>
       <c r="CA15" s="34">
@@ -5142,32 +5668,32 @@
         <v>4.1550925925925913E-3</v>
       </c>
       <c r="CB15" s="32"/>
-      <c r="CC15" s="83"/>
+      <c r="CC15" s="78"/>
       <c r="CD15" s="34" t="str">
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE15" s="32"/>
-      <c r="CF15" s="83"/>
+      <c r="CF15" s="78"/>
       <c r="CG15" s="34" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
-      <c r="CH15" s="32">
+      <c r="CH15" s="32"/>
+      <c r="CI15" s="78"/>
+      <c r="CJ15" s="34" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CK15" s="32">
         <v>1</v>
       </c>
-      <c r="CI15" s="83">
+      <c r="CL15" s="78">
         <v>1.0289351851851852E-2</v>
       </c>
-      <c r="CJ15" s="34">
-        <f t="shared" si="17"/>
+      <c r="CM15" s="34">
+        <f t="shared" si="18"/>
         <v>4.409722222222222E-3</v>
-      </c>
-      <c r="CK15" s="32"/>
-      <c r="CL15" s="33"/>
-      <c r="CM15" s="34" t="str">
-        <f t="shared" si="18"/>
-        <v>NA</v>
       </c>
       <c r="CN15" s="32"/>
       <c r="CO15" s="33"/>
@@ -5196,12 +5722,46 @@
       <c r="CZ15" s="32"/>
       <c r="DA15" s="33"/>
       <c r="DB15" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v>NA</v>
-      </c>
-      <c r="DC15" s="37"/>
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC15" s="32"/>
+      <c r="DD15" s="33"/>
+      <c r="DE15" s="34" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF15" s="32"/>
+      <c r="DG15" s="33"/>
+      <c r="DH15" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI15" s="32">
+        <v>3</v>
+      </c>
+      <c r="DJ15" s="35">
+        <v>5.9027777777777776E-3</v>
+      </c>
+      <c r="DK15" s="34">
+        <f t="shared" si="26"/>
+        <v>2.3148148148148008E-5</v>
+      </c>
+      <c r="DL15" s="32"/>
+      <c r="DM15" s="33"/>
+      <c r="DN15" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO15" s="32"/>
+      <c r="DP15" s="33"/>
+      <c r="DQ15" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DR15" s="37"/>
     </row>
-    <row r="16" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>208</v>
       </c>
@@ -5218,7 +5778,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>E5</v>
       </c>
       <c r="G16" s="5">
@@ -5282,7 +5842,7 @@
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
       <c r="AC16" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>4.7905092592592589E-2</v>
       </c>
       <c r="AD16" s="20">
@@ -5292,7 +5852,7 @@
         <v>1.3888888888888889E-3</v>
       </c>
       <c r="AF16" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>4.1932870370370363E-2</v>
       </c>
       <c r="AG16" s="21">
@@ -5303,21 +5863,21 @@
       </c>
       <c r="AI16" s="22"/>
       <c r="AJ16" s="30">
+        <v>5</v>
+      </c>
+      <c r="AK16" s="31">
         <v>4</v>
-      </c>
-      <c r="AK16" s="31">
-        <v>3</v>
       </c>
       <c r="AL16" s="32"/>
       <c r="AM16" s="35"/>
       <c r="AN16" s="34" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO16" s="32"/>
       <c r="AP16" s="35"/>
       <c r="AQ16" s="34" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AR16" s="32">
@@ -5327,13 +5887,13 @@
         <v>3.0555555555555555E-2</v>
       </c>
       <c r="AT16" s="34">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>2.5972222222222223E-2</v>
       </c>
       <c r="AU16" s="32"/>
       <c r="AV16" s="35"/>
       <c r="AW16" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="32"/>
@@ -5345,51 +5905,51 @@
       <c r="BA16" s="32"/>
       <c r="BB16" s="35"/>
       <c r="BC16" s="34" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="BD16" s="32"/>
       <c r="BE16" s="35"/>
       <c r="BF16" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG16" s="32"/>
       <c r="BH16" s="35"/>
       <c r="BI16" s="34" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
-      <c r="BJ16" s="43">
+        <f t="shared" si="38"/>
+        <v>NA</v>
+      </c>
+      <c r="BJ16" s="32">
         <v>12</v>
       </c>
-      <c r="BK16" s="90">
+      <c r="BK16" s="81">
         <v>5.7407407407407416E-3</v>
       </c>
       <c r="BL16" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>1.1574074074074082E-3</v>
       </c>
       <c r="BM16" s="32"/>
       <c r="BN16" s="33"/>
       <c r="BO16" s="34" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP16" s="32"/>
       <c r="BQ16" s="33"/>
       <c r="BR16" s="34" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="32">
         <v>1</v>
       </c>
-      <c r="BT16" s="69">
+      <c r="BT16" s="64">
         <v>3.1041666666666665E-2</v>
       </c>
       <c r="BU16" s="34">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>2.6458333333333334E-2</v>
       </c>
       <c r="BV16" s="32"/>
@@ -5398,8 +5958,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY16" s="86"/>
-      <c r="BZ16" s="69"/>
+      <c r="BY16" s="33"/>
+      <c r="BZ16" s="64"/>
       <c r="CA16" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -5455,12 +6015,50 @@
       <c r="CZ16" s="32"/>
       <c r="DA16" s="35"/>
       <c r="DB16" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v>NA</v>
-      </c>
-      <c r="DC16" s="37"/>
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC16" s="32">
+        <v>1</v>
+      </c>
+      <c r="DD16" s="35">
+        <v>5.6365740740740742E-3</v>
+      </c>
+      <c r="DE16" s="34">
+        <f t="shared" si="24"/>
+        <v>1.0532407407407409E-3</v>
+      </c>
+      <c r="DF16" s="32"/>
+      <c r="DG16" s="35"/>
+      <c r="DH16" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI16" s="32">
+        <v>1</v>
+      </c>
+      <c r="DJ16" s="35">
+        <v>5.0462962962962961E-3</v>
+      </c>
+      <c r="DK16" s="34">
+        <f t="shared" si="26"/>
+        <v>4.6296296296296276E-4</v>
+      </c>
+      <c r="DL16" s="32"/>
+      <c r="DM16" s="35"/>
+      <c r="DN16" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO16" s="32"/>
+      <c r="DP16" s="35"/>
+      <c r="DQ16" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DR16" s="37"/>
     </row>
-    <row r="17" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>208</v>
       </c>
@@ -5477,7 +6075,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>L6</v>
       </c>
       <c r="G17" s="5">
@@ -5537,7 +6135,7 @@
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>5.7766203703703708E-2</v>
       </c>
       <c r="AD17" s="20">
@@ -5547,7 +6145,7 @@
         <v>7.9861111111111122E-3</v>
       </c>
       <c r="AF17" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>4.2488425925925929E-2</v>
       </c>
       <c r="AG17" s="21">
@@ -5566,7 +6164,7 @@
       <c r="AL17" s="32"/>
       <c r="AM17" s="35"/>
       <c r="AN17" s="34" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO17" s="32">
@@ -5576,7 +6174,7 @@
         <v>4.2083333333333334E-2</v>
       </c>
       <c r="AQ17" s="34">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>3.4791666666666665E-2</v>
       </c>
       <c r="AR17" s="32">
@@ -5586,13 +6184,13 @@
         <v>2.5196759259259256E-2</v>
       </c>
       <c r="AT17" s="34">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>1.7905092592592591E-2</v>
       </c>
       <c r="AU17" s="32"/>
       <c r="AV17" s="35"/>
       <c r="AW17" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="32"/>
@@ -5608,43 +6206,43 @@
         <v>3.3854166666666664E-2</v>
       </c>
       <c r="BC17" s="34">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>2.6562499999999999E-2</v>
       </c>
       <c r="BD17" s="32"/>
       <c r="BE17" s="35"/>
       <c r="BF17" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG17" s="32"/>
       <c r="BH17" s="35"/>
       <c r="BI17" s="34" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
-      <c r="BJ17" s="43"/>
+        <f t="shared" si="38"/>
+        <v>NA</v>
+      </c>
+      <c r="BJ17" s="32"/>
       <c r="BK17" s="35"/>
       <c r="BL17" s="34" t="str">
-        <f t="shared" si="34"/>
-        <v>NA</v>
-      </c>
-      <c r="BM17" s="43"/>
+        <f t="shared" si="39"/>
+        <v>NA</v>
+      </c>
+      <c r="BM17" s="32"/>
       <c r="BN17" s="35"/>
       <c r="BO17" s="34" t="str">
-        <f t="shared" si="35"/>
-        <v>NA</v>
-      </c>
-      <c r="BP17" s="43"/>
+        <f t="shared" si="40"/>
+        <v>NA</v>
+      </c>
+      <c r="BP17" s="32"/>
       <c r="BQ17" s="35"/>
       <c r="BR17" s="34" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS17" s="32"/>
       <c r="BT17" s="33"/>
       <c r="BU17" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV17" s="32"/>
@@ -5653,8 +6251,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY17" s="86"/>
-      <c r="BZ17" s="69"/>
+      <c r="BY17" s="33"/>
+      <c r="BZ17" s="64"/>
       <c r="CA17" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -5707,19 +6305,53 @@
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ17" s="32">
+      <c r="CZ17" s="32"/>
+      <c r="DA17" s="35"/>
+      <c r="DB17" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC17" s="32">
         <v>2</v>
       </c>
-      <c r="DA17" s="35">
+      <c r="DD17" s="35">
         <v>0.80208333333333337</v>
       </c>
-      <c r="DB17" s="34">
-        <f t="shared" si="38"/>
+      <c r="DE17" s="34">
+        <f t="shared" si="24"/>
         <v>0.79479166666666667</v>
       </c>
-      <c r="DC17" s="37"/>
+      <c r="DF17" s="32">
+        <v>1</v>
+      </c>
+      <c r="DG17" s="35">
+        <v>2.5937499999999999E-2</v>
+      </c>
+      <c r="DH17" s="34">
+        <f t="shared" si="25"/>
+        <v>1.8645833333333334E-2</v>
+      </c>
+      <c r="DI17" s="32"/>
+      <c r="DJ17" s="35"/>
+      <c r="DK17" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL17" s="32"/>
+      <c r="DM17" s="35"/>
+      <c r="DN17" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO17" s="32"/>
+      <c r="DP17" s="35"/>
+      <c r="DQ17" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DR17" s="37"/>
     </row>
-    <row r="18" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>208</v>
       </c>
@@ -5736,7 +6368,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>D4</v>
       </c>
       <c r="G18" s="5">
@@ -5798,7 +6430,7 @@
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>5.6296296296296289E-2</v>
       </c>
       <c r="AD18" s="20">
@@ -5808,7 +6440,7 @@
         <v>9.2361111111111116E-3</v>
       </c>
       <c r="AF18" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>4.2905092592592585E-2</v>
       </c>
       <c r="AG18" s="21">
@@ -5827,7 +6459,7 @@
       <c r="AL18" s="32"/>
       <c r="AM18" s="35"/>
       <c r="AN18" s="34" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO18" s="32">
@@ -5837,19 +6469,19 @@
         <v>2.3078703703703702E-2</v>
       </c>
       <c r="AQ18" s="34">
-        <f t="shared" si="28"/>
+        <f t="shared" si="33"/>
         <v>1.892361111111111E-2</v>
       </c>
       <c r="AR18" s="32"/>
       <c r="AS18" s="35"/>
       <c r="AT18" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AU18" s="32"/>
       <c r="AV18" s="35"/>
       <c r="AW18" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX18" s="32"/>
@@ -5865,43 +6497,43 @@
         <v>1.3321759259259261E-2</v>
       </c>
       <c r="BC18" s="34">
-        <f t="shared" si="31"/>
+        <f t="shared" si="36"/>
         <v>9.1666666666666667E-3</v>
       </c>
       <c r="BD18" s="32"/>
       <c r="BE18" s="35"/>
       <c r="BF18" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG18" s="32"/>
       <c r="BH18" s="35"/>
       <c r="BI18" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="32"/>
       <c r="BK18" s="35"/>
       <c r="BL18" s="34" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BM18" s="32"/>
       <c r="BN18" s="35"/>
       <c r="BO18" s="34" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP18" s="32"/>
       <c r="BQ18" s="35"/>
       <c r="BR18" s="34" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="32"/>
       <c r="BT18" s="33"/>
       <c r="BU18" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV18" s="32"/>
@@ -5910,8 +6542,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY18" s="86"/>
-      <c r="BZ18" s="69"/>
+      <c r="BY18" s="33"/>
+      <c r="BZ18" s="64"/>
       <c r="CA18" s="34" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -5964,19 +6596,49 @@
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ18" s="32">
+      <c r="CZ18" s="32"/>
+      <c r="DA18" s="35"/>
+      <c r="DB18" s="34" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC18" s="32">
         <v>3</v>
       </c>
-      <c r="DA18" s="35">
+      <c r="DD18" s="35">
         <v>4.2245370370370371E-3</v>
       </c>
-      <c r="DB18" s="34">
-        <f t="shared" si="38"/>
+      <c r="DE18" s="34">
+        <f t="shared" si="24"/>
         <v>6.9444444444444024E-5</v>
       </c>
-      <c r="DC18" s="37"/>
+      <c r="DF18" s="32"/>
+      <c r="DG18" s="35"/>
+      <c r="DH18" s="34" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI18" s="32"/>
+      <c r="DJ18" s="35"/>
+      <c r="DK18" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL18" s="32"/>
+      <c r="DM18" s="35"/>
+      <c r="DN18" s="34" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO18" s="32"/>
+      <c r="DP18" s="35"/>
+      <c r="DQ18" s="34" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DR18" s="37"/>
     </row>
-    <row r="19" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>208</v>
       </c>
@@ -5993,7 +6655,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>L5</v>
       </c>
       <c r="G19" s="5">
@@ -6055,7 +6717,7 @@
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>5.2766203703703704E-2</v>
       </c>
       <c r="AD19" s="20">
@@ -6063,7 +6725,7 @@
       </c>
       <c r="AE19" s="20"/>
       <c r="AF19" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>3.5868055555555556E-2</v>
       </c>
       <c r="AG19" s="21">
@@ -6081,8 +6743,8 @@
       </c>
       <c r="AL19" s="33"/>
       <c r="AM19" s="35"/>
-      <c r="AN19" s="69" t="str">
-        <f t="shared" si="27"/>
+      <c r="AN19" s="64" t="str">
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO19" s="33">
@@ -6091,25 +6753,25 @@
       <c r="AP19" s="35">
         <v>1.2</v>
       </c>
-      <c r="AQ19" s="69">
-        <f t="shared" si="28"/>
+      <c r="AQ19" s="64">
+        <f t="shared" si="33"/>
         <v>1.1831018518518519</v>
       </c>
       <c r="AR19" s="33"/>
       <c r="AS19" s="35"/>
-      <c r="AT19" s="69" t="str">
-        <f t="shared" si="29"/>
+      <c r="AT19" s="64" t="str">
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AU19" s="33"/>
       <c r="AV19" s="35"/>
-      <c r="AW19" s="69" t="str">
-        <f t="shared" si="30"/>
+      <c r="AW19" s="64" t="str">
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX19" s="33"/>
       <c r="AY19" s="35"/>
-      <c r="AZ19" s="69" t="str">
+      <c r="AZ19" s="64" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
@@ -6119,119 +6781,157 @@
       <c r="BB19" s="35">
         <v>2.2754629629629628E-2</v>
       </c>
-      <c r="BC19" s="69">
-        <f t="shared" si="31"/>
+      <c r="BC19" s="64">
+        <f t="shared" si="36"/>
         <v>5.8564814814814799E-3</v>
       </c>
       <c r="BD19" s="33"/>
       <c r="BE19" s="35"/>
-      <c r="BF19" s="69" t="str">
-        <f t="shared" si="32"/>
+      <c r="BF19" s="64" t="str">
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG19" s="33"/>
       <c r="BH19" s="35"/>
-      <c r="BI19" s="69" t="str">
-        <f t="shared" si="33"/>
+      <c r="BI19" s="64" t="str">
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="33"/>
       <c r="BK19" s="35"/>
-      <c r="BL19" s="69" t="str">
-        <f t="shared" si="34"/>
+      <c r="BL19" s="64" t="str">
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BM19" s="33"/>
       <c r="BN19" s="35"/>
-      <c r="BO19" s="69" t="str">
-        <f t="shared" si="35"/>
+      <c r="BO19" s="64" t="str">
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP19" s="33"/>
       <c r="BQ19" s="35"/>
-      <c r="BR19" s="69" t="str">
-        <f t="shared" si="36"/>
+      <c r="BR19" s="64" t="str">
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="33"/>
       <c r="BT19" s="33"/>
-      <c r="BU19" s="69" t="str">
-        <f t="shared" si="37"/>
+      <c r="BU19" s="64" t="str">
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV19" s="33"/>
       <c r="BW19" s="33"/>
-      <c r="BX19" s="69" t="str">
+      <c r="BX19" s="64" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY19" s="86"/>
-      <c r="BZ19" s="69"/>
-      <c r="CA19" s="69" t="str">
+      <c r="BY19" s="33"/>
+      <c r="BZ19" s="64"/>
+      <c r="CA19" s="64" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
       </c>
       <c r="CB19" s="33"/>
       <c r="CC19" s="35"/>
-      <c r="CD19" s="69" t="str">
+      <c r="CD19" s="64" t="str">
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE19" s="33"/>
       <c r="CF19" s="35"/>
-      <c r="CG19" s="69" t="str">
+      <c r="CG19" s="64" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CH19" s="33"/>
       <c r="CI19" s="35"/>
-      <c r="CJ19" s="69" t="str">
+      <c r="CJ19" s="64" t="str">
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CK19" s="33"/>
       <c r="CL19" s="35"/>
-      <c r="CM19" s="69" t="str">
+      <c r="CM19" s="64" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CN19" s="33"/>
       <c r="CO19" s="35"/>
-      <c r="CP19" s="69" t="str">
+      <c r="CP19" s="64" t="str">
         <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CQ19" s="33"/>
       <c r="CR19" s="35"/>
-      <c r="CS19" s="69" t="str">
+      <c r="CS19" s="64" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT19" s="33"/>
       <c r="CU19" s="35"/>
-      <c r="CV19" s="69" t="str">
+      <c r="CV19" s="64" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW19" s="33"/>
       <c r="CX19" s="35"/>
-      <c r="CY19" s="69" t="str">
+      <c r="CY19" s="64" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ19" s="33">
+      <c r="CZ19" s="33"/>
+      <c r="DA19" s="35"/>
+      <c r="DB19" s="64" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC19" s="33">
         <v>2</v>
       </c>
-      <c r="DA19" s="35">
+      <c r="DD19" s="35">
         <v>1.0895833333333333</v>
       </c>
-      <c r="DB19" s="69">
-        <f t="shared" si="38"/>
+      <c r="DE19" s="64">
+        <f t="shared" si="24"/>
         <v>1.0726851851851853</v>
       </c>
-      <c r="DC19" s="33"/>
+      <c r="DF19" s="33">
+        <v>1</v>
+      </c>
+      <c r="DG19" s="35">
+        <v>1.8807870370370371E-2</v>
+      </c>
+      <c r="DH19" s="64">
+        <f t="shared" si="25"/>
+        <v>1.9097222222222224E-3</v>
+      </c>
+      <c r="DI19" s="33"/>
+      <c r="DJ19" s="35"/>
+      <c r="DK19" s="64" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL19" s="33">
+        <v>1</v>
+      </c>
+      <c r="DM19" s="35">
+        <v>2.2847222222222224E-2</v>
+      </c>
+      <c r="DN19" s="64">
+        <f t="shared" si="27"/>
+        <v>5.9490740740740754E-3</v>
+      </c>
+      <c r="DO19" s="33"/>
+      <c r="DP19" s="35"/>
+      <c r="DQ19" s="64" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DR19" s="33"/>
     </row>
-    <row r="20" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>208</v>
       </c>
@@ -6248,7 +6948,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>D5</v>
       </c>
       <c r="G20" s="5">
@@ -6310,7 +7010,7 @@
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>6.4189814814814811E-2</v>
       </c>
       <c r="AD20" s="20">
@@ -6320,7 +7020,7 @@
         <v>1.5046296296296295E-2</v>
       </c>
       <c r="AF20" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>4.4687499999999998E-2</v>
       </c>
       <c r="AG20" s="21">
@@ -6338,31 +7038,31 @@
       </c>
       <c r="AL20" s="33"/>
       <c r="AM20" s="35"/>
-      <c r="AN20" s="69" t="str">
-        <f t="shared" si="27"/>
+      <c r="AN20" s="64" t="str">
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO20" s="33"/>
       <c r="AP20" s="35"/>
-      <c r="AQ20" s="69" t="str">
-        <f t="shared" si="28"/>
+      <c r="AQ20" s="64" t="str">
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AR20" s="33"/>
       <c r="AS20" s="35"/>
-      <c r="AT20" s="69" t="str">
-        <f t="shared" si="29"/>
+      <c r="AT20" s="64" t="str">
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AU20" s="33"/>
       <c r="AV20" s="35"/>
-      <c r="AW20" s="69" t="str">
-        <f t="shared" si="30"/>
+      <c r="AW20" s="64" t="str">
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX20" s="33"/>
       <c r="AY20" s="35"/>
-      <c r="AZ20" s="69" t="str">
+      <c r="AZ20" s="64" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
@@ -6372,119 +7072,153 @@
       <c r="BB20" s="35">
         <v>3.050925925925926E-2</v>
       </c>
-      <c r="BC20" s="69">
-        <f t="shared" si="31"/>
+      <c r="BC20" s="64">
+        <f t="shared" si="36"/>
         <v>2.6053240740740741E-2</v>
       </c>
       <c r="BD20" s="33"/>
       <c r="BE20" s="35"/>
-      <c r="BF20" s="69" t="str">
-        <f t="shared" si="32"/>
+      <c r="BF20" s="64" t="str">
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG20" s="33"/>
       <c r="BH20" s="35"/>
-      <c r="BI20" s="69" t="str">
-        <f t="shared" si="33"/>
+      <c r="BI20" s="64" t="str">
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ20" s="33"/>
       <c r="BK20" s="35"/>
-      <c r="BL20" s="69" t="str">
-        <f t="shared" si="34"/>
+      <c r="BL20" s="64" t="str">
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BM20" s="33"/>
       <c r="BN20" s="35"/>
-      <c r="BO20" s="69" t="str">
-        <f t="shared" si="35"/>
+      <c r="BO20" s="64" t="str">
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP20" s="33"/>
       <c r="BQ20" s="35"/>
-      <c r="BR20" s="69" t="str">
-        <f t="shared" si="36"/>
+      <c r="BR20" s="64" t="str">
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS20" s="33"/>
       <c r="BT20" s="35"/>
-      <c r="BU20" s="69" t="str">
-        <f t="shared" si="37"/>
+      <c r="BU20" s="64" t="str">
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV20" s="33"/>
       <c r="BW20" s="35"/>
-      <c r="BX20" s="69" t="str">
+      <c r="BX20" s="64" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY20" s="86"/>
-      <c r="BZ20" s="69"/>
-      <c r="CA20" s="69" t="str">
+      <c r="BY20" s="33"/>
+      <c r="BZ20" s="64"/>
+      <c r="CA20" s="64" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
       </c>
       <c r="CB20" s="33"/>
       <c r="CC20" s="35"/>
-      <c r="CD20" s="69" t="str">
+      <c r="CD20" s="64" t="str">
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE20" s="33"/>
       <c r="CF20" s="35"/>
-      <c r="CG20" s="69" t="str">
+      <c r="CG20" s="64" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CH20" s="33"/>
       <c r="CI20" s="35"/>
-      <c r="CJ20" s="69" t="str">
+      <c r="CJ20" s="64" t="str">
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CK20" s="33"/>
       <c r="CL20" s="35"/>
-      <c r="CM20" s="69" t="str">
+      <c r="CM20" s="64" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CN20" s="33"/>
       <c r="CO20" s="35"/>
-      <c r="CP20" s="69" t="str">
+      <c r="CP20" s="64" t="str">
         <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CQ20" s="33"/>
       <c r="CR20" s="35"/>
-      <c r="CS20" s="69" t="str">
+      <c r="CS20" s="64" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT20" s="33"/>
       <c r="CU20" s="35"/>
-      <c r="CV20" s="69" t="str">
+      <c r="CV20" s="64" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW20" s="33"/>
       <c r="CX20" s="35"/>
-      <c r="CY20" s="69" t="str">
+      <c r="CY20" s="64" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ20" s="33">
+      <c r="CZ20" s="33"/>
+      <c r="DA20" s="35"/>
+      <c r="DB20" s="64" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC20" s="33">
         <v>1</v>
       </c>
-      <c r="DA20" s="35">
+      <c r="DD20" s="35">
         <v>3.3784722222222223E-2</v>
       </c>
-      <c r="DB20" s="69">
-        <f t="shared" si="38"/>
+      <c r="DE20" s="64">
+        <f t="shared" si="24"/>
         <v>2.9328703703703704E-2</v>
       </c>
-      <c r="DC20" s="33"/>
+      <c r="DF20" s="33"/>
+      <c r="DG20" s="35"/>
+      <c r="DH20" s="64" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI20" s="33">
+        <v>2</v>
+      </c>
+      <c r="DJ20" s="35">
+        <v>5.115740740740741E-3</v>
+      </c>
+      <c r="DK20" s="64">
+        <f t="shared" si="26"/>
+        <v>6.5972222222222213E-4</v>
+      </c>
+      <c r="DL20" s="33"/>
+      <c r="DM20" s="35"/>
+      <c r="DN20" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO20" s="33"/>
+      <c r="DP20" s="35"/>
+      <c r="DQ20" s="64" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DR20" s="33"/>
     </row>
-    <row r="21" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>208</v>
       </c>
@@ -6501,7 +7235,7 @@
         <v>6</v>
       </c>
       <c r="F21" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>D6</v>
       </c>
       <c r="G21" s="5">
@@ -6510,10 +7244,10 @@
       <c r="H21" s="5">
         <v>14</v>
       </c>
-      <c r="I21" s="64">
+      <c r="I21" s="6">
         <v>0.6</v>
       </c>
-      <c r="J21" s="64">
+      <c r="J21" s="6">
         <v>0.64861111111111114</v>
       </c>
       <c r="K21" s="7">
@@ -6530,226 +7264,272 @@
       <c r="N21" s="5">
         <v>22</v>
       </c>
-      <c r="O21" s="65" t="s">
+      <c r="O21" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="P21" s="65">
+      <c r="P21" s="5">
         <v>3</v>
       </c>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="65" t="s">
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5" t="s">
         <v>123</v>
       </c>
       <c r="S21" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="T21" s="65">
+      <c r="T21" s="5">
         <v>0.28000000000000003</v>
       </c>
-      <c r="U21" s="65" t="s">
+      <c r="U21" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="V21" s="65"/>
-      <c r="W21" s="66">
+      <c r="V21" s="5"/>
+      <c r="W21" s="63">
         <v>1.9675925925925926E-4</v>
       </c>
-      <c r="X21" s="66">
+      <c r="X21" s="63">
         <v>2.6377314814814815E-2</v>
       </c>
-      <c r="Y21" s="66">
+      <c r="Y21" s="63">
         <v>2.3043981481481481E-2</v>
       </c>
-      <c r="Z21" s="66"/>
-      <c r="AA21" s="66"/>
-      <c r="AB21" s="66"/>
+      <c r="Z21" s="63"/>
+      <c r="AA21" s="63"/>
+      <c r="AB21" s="63"/>
       <c r="AC21" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="30"/>
         <v>4.9618055555555554E-2</v>
       </c>
-      <c r="AD21" s="91">
+      <c r="AD21" s="82">
         <v>4.363425925925926E-3</v>
       </c>
-      <c r="AE21" s="91">
+      <c r="AE21" s="82">
         <v>2.3148148148148146E-4</v>
       </c>
       <c r="AF21" s="20">
-        <f t="shared" si="26"/>
+        <f t="shared" si="31"/>
         <v>4.5023148148148152E-2</v>
       </c>
-      <c r="AG21" s="67">
+      <c r="AG21" s="21">
         <v>100</v>
       </c>
-      <c r="AH21" s="67">
+      <c r="AH21" s="21">
         <v>75</v>
       </c>
-      <c r="AI21" s="67"/>
-      <c r="AJ21" s="68">
-        <v>6</v>
-      </c>
-      <c r="AK21" s="68">
-        <v>4</v>
-      </c>
-      <c r="AL21" s="68"/>
-      <c r="AM21" s="68"/>
-      <c r="AN21" s="69" t="str">
-        <f t="shared" si="27"/>
-        <v>NA</v>
-      </c>
-      <c r="AO21" s="68"/>
-      <c r="AP21" s="68"/>
-      <c r="AQ21" s="69" t="str">
-        <f t="shared" si="28"/>
-        <v>NA</v>
-      </c>
-      <c r="AR21" s="68"/>
-      <c r="AS21" s="68"/>
-      <c r="AT21" s="69" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
-      </c>
-      <c r="AU21" s="68"/>
-      <c r="AV21" s="68"/>
-      <c r="AW21" s="69" t="str">
-        <f t="shared" si="30"/>
-        <v>NA</v>
-      </c>
-      <c r="AX21" s="68"/>
-      <c r="AY21" s="68"/>
-      <c r="AZ21" s="69" t="str">
+      <c r="AI21" s="21"/>
+      <c r="AJ21" s="33">
+        <v>7</v>
+      </c>
+      <c r="AK21" s="33">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="33">
+        <v>1</v>
+      </c>
+      <c r="AM21" s="35">
+        <v>2.0254629629629629E-2</v>
+      </c>
+      <c r="AN21" s="64">
+        <f t="shared" si="32"/>
+        <v>1.5891203703703703E-2</v>
+      </c>
+      <c r="AO21" s="33">
+        <v>1</v>
+      </c>
+      <c r="AP21" s="35">
+        <v>4.9166666666666664E-2</v>
+      </c>
+      <c r="AQ21" s="64">
+        <f t="shared" si="33"/>
+        <v>4.4803240740740741E-2</v>
+      </c>
+      <c r="AR21" s="33"/>
+      <c r="AS21" s="33"/>
+      <c r="AT21" s="64" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="AU21" s="33"/>
+      <c r="AV21" s="33"/>
+      <c r="AW21" s="64" t="str">
+        <f t="shared" si="35"/>
+        <v>NA</v>
+      </c>
+      <c r="AX21" s="33"/>
+      <c r="AY21" s="33"/>
+      <c r="AZ21" s="64" t="str">
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="BA21" s="68">
+      <c r="BA21" s="33">
         <v>1</v>
       </c>
-      <c r="BB21" s="92">
+      <c r="BB21" s="35">
         <v>5.4398148148148149E-3</v>
       </c>
-      <c r="BC21" s="69">
-        <f t="shared" si="31"/>
+      <c r="BC21" s="64">
+        <f t="shared" si="36"/>
         <v>1.0763888888888889E-3</v>
       </c>
-      <c r="BD21" s="68"/>
-      <c r="BE21" s="68"/>
-      <c r="BF21" s="69" t="str">
-        <f t="shared" si="32"/>
-        <v>NA</v>
-      </c>
-      <c r="BG21" s="68"/>
-      <c r="BH21" s="68"/>
-      <c r="BI21" s="69" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
-      <c r="BJ21" s="68">
+      <c r="BD21" s="33"/>
+      <c r="BE21" s="33"/>
+      <c r="BF21" s="64" t="str">
+        <f t="shared" si="37"/>
+        <v>NA</v>
+      </c>
+      <c r="BG21" s="33"/>
+      <c r="BH21" s="33"/>
+      <c r="BI21" s="64" t="str">
+        <f t="shared" si="38"/>
+        <v>NA</v>
+      </c>
+      <c r="BJ21" s="33">
         <v>1</v>
       </c>
-      <c r="BK21" s="93">
+      <c r="BK21" s="64">
         <v>1.1743055555555555</v>
       </c>
-      <c r="BL21" s="69">
-        <f t="shared" si="34"/>
+      <c r="BL21" s="64">
+        <f t="shared" si="39"/>
         <v>1.1699421296296295</v>
       </c>
-      <c r="BM21" s="68"/>
-      <c r="BN21" s="68"/>
-      <c r="BO21" s="69" t="str">
-        <f t="shared" si="35"/>
-        <v>NA</v>
-      </c>
-      <c r="BP21" s="68"/>
-      <c r="BQ21" s="68"/>
-      <c r="BR21" s="69" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="BS21" s="68"/>
-      <c r="BT21" s="68"/>
-      <c r="BU21" s="69" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="BV21" s="68"/>
-      <c r="BW21" s="68"/>
-      <c r="BX21" s="69" t="str">
+      <c r="BM21" s="33"/>
+      <c r="BN21" s="33"/>
+      <c r="BO21" s="64" t="str">
+        <f t="shared" si="40"/>
+        <v>NA</v>
+      </c>
+      <c r="BP21" s="33"/>
+      <c r="BQ21" s="33"/>
+      <c r="BR21" s="64" t="str">
+        <f t="shared" si="41"/>
+        <v>NA</v>
+      </c>
+      <c r="BS21" s="33"/>
+      <c r="BT21" s="33"/>
+      <c r="BU21" s="64" t="str">
+        <f t="shared" si="42"/>
+        <v>NA</v>
+      </c>
+      <c r="BV21" s="33"/>
+      <c r="BW21" s="33"/>
+      <c r="BX21" s="64" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY21" s="87">
+      <c r="BY21" s="33">
         <v>1</v>
       </c>
-      <c r="BZ21" s="92">
+      <c r="BZ21" s="35">
         <v>2.2418981481481481E-2</v>
       </c>
-      <c r="CA21" s="69">
+      <c r="CA21" s="64">
         <f t="shared" si="14"/>
         <v>1.8055555555555554E-2</v>
       </c>
-      <c r="CB21" s="68"/>
-      <c r="CC21" s="68"/>
-      <c r="CD21" s="69" t="str">
+      <c r="CB21" s="33"/>
+      <c r="CC21" s="33"/>
+      <c r="CD21" s="64" t="str">
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE21" s="68"/>
-      <c r="CF21" s="68"/>
-      <c r="CG21" s="69" t="str">
+      <c r="CE21" s="33"/>
+      <c r="CF21" s="33"/>
+      <c r="CG21" s="64" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
-      <c r="CH21" s="68"/>
-      <c r="CI21" s="68"/>
-      <c r="CJ21" s="69" t="str">
+      <c r="CH21" s="33"/>
+      <c r="CI21" s="33"/>
+      <c r="CJ21" s="64" t="str">
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
-      <c r="CK21" s="68"/>
-      <c r="CL21" s="68"/>
-      <c r="CM21" s="69" t="str">
+      <c r="CK21" s="33"/>
+      <c r="CL21" s="33"/>
+      <c r="CM21" s="64" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
       </c>
-      <c r="CN21" s="68"/>
-      <c r="CO21" s="68"/>
-      <c r="CP21" s="69" t="str">
+      <c r="CN21" s="33"/>
+      <c r="CO21" s="33"/>
+      <c r="CP21" s="64" t="str">
         <f t="shared" si="19"/>
         <v>NA</v>
       </c>
-      <c r="CQ21" s="68"/>
-      <c r="CR21" s="68"/>
-      <c r="CS21" s="69" t="str">
+      <c r="CQ21" s="33"/>
+      <c r="CR21" s="33"/>
+      <c r="CS21" s="64" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
-      <c r="CT21" s="68"/>
-      <c r="CU21" s="68"/>
-      <c r="CV21" s="69" t="str">
+      <c r="CT21" s="33"/>
+      <c r="CU21" s="33"/>
+      <c r="CV21" s="64" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW21" s="68">
+      <c r="CW21" s="33"/>
+      <c r="CX21" s="33"/>
+      <c r="CY21" s="64" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ21" s="33">
         <v>1</v>
       </c>
-      <c r="CX21" s="93">
+      <c r="DA21" s="64">
         <v>1.2305555555555556</v>
       </c>
-      <c r="CY21" s="69">
-        <f t="shared" si="22"/>
+      <c r="DB21" s="64">
+        <f t="shared" si="23"/>
         <v>1.2261921296296296</v>
       </c>
-      <c r="CZ21" s="68">
+      <c r="DC21" s="33">
         <v>1</v>
       </c>
-      <c r="DA21" s="93">
-        <v>1.4541666666666666</v>
-      </c>
-      <c r="DB21" s="69">
-        <f t="shared" si="38"/>
-        <v>1.4498032407407406</v>
-      </c>
-      <c r="DC21" s="68"/>
+      <c r="DD21" s="64">
+        <v>6.7939814814814816E-3</v>
+      </c>
+      <c r="DE21" s="64">
+        <f t="shared" si="24"/>
+        <v>2.4305555555555556E-3</v>
+      </c>
+      <c r="DF21" s="33">
+        <v>1</v>
+      </c>
+      <c r="DG21" s="64">
+        <v>7.3495370370370372E-3</v>
+      </c>
+      <c r="DH21" s="64">
+        <f t="shared" si="25"/>
+        <v>2.9861111111111113E-3</v>
+      </c>
+      <c r="DI21" s="33">
+        <v>1</v>
+      </c>
+      <c r="DJ21" s="64">
+        <v>3.8206018518518521E-2</v>
+      </c>
+      <c r="DK21" s="64">
+        <f t="shared" si="26"/>
+        <v>3.3842592592592598E-2</v>
+      </c>
+      <c r="DL21" s="33"/>
+      <c r="DM21" s="64"/>
+      <c r="DN21" s="64" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO21" s="33"/>
+      <c r="DP21" s="64"/>
+      <c r="DQ21" s="64" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DR21" s="33"/>
     </row>
-    <row r="22" spans="1:107" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>208</v>
       </c>
@@ -6766,7 +7546,7 @@
         <v>4</v>
       </c>
       <c r="F22" s="5" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="29"/>
         <v>L4</v>
       </c>
       <c r="G22" s="5">
@@ -6775,10 +7555,10 @@
       <c r="H22" s="5">
         <v>5</v>
       </c>
-      <c r="I22" s="64">
+      <c r="I22" s="6">
         <v>0.59583333333333333</v>
       </c>
-      <c r="J22" s="64">
+      <c r="J22" s="6">
         <v>0.64652777777777781</v>
       </c>
       <c r="K22" s="7">
@@ -6795,226 +7575,272 @@
       <c r="N22" s="5">
         <v>30</v>
       </c>
-      <c r="O22" s="65" t="s">
+      <c r="O22" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="P22" s="65">
+      <c r="P22" s="5">
         <v>2</v>
       </c>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65" t="s">
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5" t="s">
         <v>109</v>
       </c>
       <c r="S22" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="T22" s="65">
+      <c r="T22" s="5">
         <v>0.28000000000000003</v>
       </c>
-      <c r="U22" s="65" t="s">
+      <c r="U22" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="V22" s="65"/>
-      <c r="W22" s="66">
+      <c r="V22" s="5"/>
+      <c r="W22" s="63">
         <v>2.8020833333333332E-2</v>
       </c>
-      <c r="X22" s="66">
+      <c r="X22" s="63">
         <v>2.3090277777777779E-2</v>
       </c>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
+      <c r="Y22" s="63"/>
+      <c r="Z22" s="63"/>
+      <c r="AA22" s="63"/>
+      <c r="AB22" s="63"/>
       <c r="AC22" s="20">
+        <f t="shared" si="30"/>
+        <v>5.1111111111111107E-2</v>
+      </c>
+      <c r="AD22" s="82">
+        <v>3.645833333333333E-3</v>
+      </c>
+      <c r="AE22" s="82">
+        <v>6.4004629629629628E-3</v>
+      </c>
+      <c r="AF22" s="20">
+        <f t="shared" si="31"/>
+        <v>4.1064814814814811E-2</v>
+      </c>
+      <c r="AG22" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH22" s="21">
+        <v>95</v>
+      </c>
+      <c r="AI22" s="21"/>
+      <c r="AJ22" s="33">
+        <v>9</v>
+      </c>
+      <c r="AK22" s="33">
+        <v>6</v>
+      </c>
+      <c r="AL22" s="33">
+        <v>6</v>
+      </c>
+      <c r="AM22" s="35">
+        <v>3.8541666666666668E-3</v>
+      </c>
+      <c r="AN22" s="64">
+        <f t="shared" si="32"/>
+        <v>2.0833333333333381E-4</v>
+      </c>
+      <c r="AO22" s="33">
+        <v>3</v>
+      </c>
+      <c r="AP22" s="35">
+        <v>3.7384259259259263E-3</v>
+      </c>
+      <c r="AQ22" s="64">
+        <f t="shared" si="33"/>
+        <v>9.2592592592593333E-5</v>
+      </c>
+      <c r="AR22" s="33"/>
+      <c r="AS22" s="33"/>
+      <c r="AT22" s="64" t="str">
+        <f t="shared" si="34"/>
+        <v>NA</v>
+      </c>
+      <c r="AU22" s="33"/>
+      <c r="AV22" s="33"/>
+      <c r="AW22" s="64" t="str">
+        <f t="shared" si="35"/>
+        <v>NA</v>
+      </c>
+      <c r="AX22" s="33">
+        <v>1</v>
+      </c>
+      <c r="AY22" s="35">
+        <v>1.4050925925925927E-2</v>
+      </c>
+      <c r="AZ22" s="64">
+        <f t="shared" si="5"/>
+        <v>1.0405092592592594E-2</v>
+      </c>
+      <c r="BA22" s="33">
+        <v>1</v>
+      </c>
+      <c r="BB22" s="35">
+        <v>1.7361111111111112E-2</v>
+      </c>
+      <c r="BC22" s="64">
+        <f t="shared" si="36"/>
+        <v>1.3715277777777779E-2</v>
+      </c>
+      <c r="BD22" s="33"/>
+      <c r="BE22" s="33"/>
+      <c r="BF22" s="64" t="str">
+        <f t="shared" si="37"/>
+        <v>NA</v>
+      </c>
+      <c r="BG22" s="33"/>
+      <c r="BH22" s="33"/>
+      <c r="BI22" s="64" t="str">
+        <f t="shared" si="38"/>
+        <v>NA</v>
+      </c>
+      <c r="BJ22" s="33">
+        <v>1</v>
+      </c>
+      <c r="BK22" s="35">
+        <v>2.732638888888889E-2</v>
+      </c>
+      <c r="BL22" s="64">
+        <f t="shared" si="39"/>
+        <v>2.3680555555555555E-2</v>
+      </c>
+      <c r="BM22" s="33"/>
+      <c r="BN22" s="33"/>
+      <c r="BO22" s="64" t="str">
+        <f t="shared" si="40"/>
+        <v>NA</v>
+      </c>
+      <c r="BP22" s="33"/>
+      <c r="BQ22" s="33"/>
+      <c r="BR22" s="64" t="str">
+        <f t="shared" si="41"/>
+        <v>NA</v>
+      </c>
+      <c r="BS22" s="33"/>
+      <c r="BT22" s="33"/>
+      <c r="BU22" s="64" t="str">
+        <f t="shared" si="42"/>
+        <v>NA</v>
+      </c>
+      <c r="BV22" s="33"/>
+      <c r="BW22" s="33"/>
+      <c r="BX22" s="64" t="str">
+        <f t="shared" si="13"/>
+        <v>NA</v>
+      </c>
+      <c r="BY22" s="33"/>
+      <c r="BZ22" s="33"/>
+      <c r="CA22" s="64" t="str">
+        <f t="shared" si="14"/>
+        <v>NA</v>
+      </c>
+      <c r="CB22" s="33"/>
+      <c r="CC22" s="33"/>
+      <c r="CD22" s="64" t="str">
+        <f t="shared" si="15"/>
+        <v>NA</v>
+      </c>
+      <c r="CE22" s="33"/>
+      <c r="CF22" s="33"/>
+      <c r="CG22" s="64" t="str">
+        <f t="shared" si="16"/>
+        <v>NA</v>
+      </c>
+      <c r="CH22" s="33"/>
+      <c r="CI22" s="33"/>
+      <c r="CJ22" s="64" t="str">
+        <f t="shared" si="17"/>
+        <v>NA</v>
+      </c>
+      <c r="CK22" s="33"/>
+      <c r="CL22" s="33"/>
+      <c r="CM22" s="64" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CN22" s="33"/>
+      <c r="CO22" s="33"/>
+      <c r="CP22" s="64" t="str">
+        <f t="shared" si="19"/>
+        <v>NA</v>
+      </c>
+      <c r="CQ22" s="33"/>
+      <c r="CR22" s="33"/>
+      <c r="CS22" s="64" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CT22" s="33"/>
+      <c r="CU22" s="33"/>
+      <c r="CV22" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CW22" s="33">
+        <v>1</v>
+      </c>
+      <c r="CX22" s="35">
+        <v>7.789351851851852E-3</v>
+      </c>
+      <c r="CY22" s="64">
+        <f t="shared" si="22"/>
+        <v>4.1435185185185186E-3</v>
+      </c>
+      <c r="CZ22" s="33"/>
+      <c r="DA22" s="35"/>
+      <c r="DB22" s="64" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DC22" s="33">
+        <v>2</v>
+      </c>
+      <c r="DD22" s="35">
+        <v>2.3541666666666666E-2</v>
+      </c>
+      <c r="DE22" s="64">
+        <f t="shared" si="24"/>
+        <v>1.9895833333333331E-2</v>
+      </c>
+      <c r="DF22" s="33">
+        <v>1</v>
+      </c>
+      <c r="DG22" s="35">
+        <v>2.6817129629629628E-2</v>
+      </c>
+      <c r="DH22" s="64">
         <f t="shared" si="25"/>
-        <v>5.1111111111111107E-2</v>
-      </c>
-      <c r="AD22" s="91">
-        <v>3.645833333333333E-3</v>
-      </c>
-      <c r="AE22" s="91">
-        <v>6.4004629629629628E-3</v>
-      </c>
-      <c r="AF22" s="20">
+        <v>2.3171296296296294E-2</v>
+      </c>
+      <c r="DI22" s="33">
+        <v>1</v>
+      </c>
+      <c r="DJ22" s="35">
+        <v>1.5393518518518518E-2</v>
+      </c>
+      <c r="DK22" s="64">
         <f t="shared" si="26"/>
-        <v>4.1064814814814811E-2</v>
-      </c>
-      <c r="AG22" s="67">
-        <v>100</v>
-      </c>
-      <c r="AH22" s="67">
-        <v>95</v>
-      </c>
-      <c r="AI22" s="67"/>
-      <c r="AJ22" s="68">
-        <v>9</v>
-      </c>
-      <c r="AK22" s="68">
-        <v>6</v>
-      </c>
-      <c r="AL22" s="68">
-        <v>6</v>
-      </c>
-      <c r="AM22" s="92">
-        <v>3.8541666666666668E-3</v>
-      </c>
-      <c r="AN22" s="69">
+        <v>1.1747685185185186E-2</v>
+      </c>
+      <c r="DL22" s="33"/>
+      <c r="DM22" s="35"/>
+      <c r="DN22" s="64" t="str">
         <f t="shared" si="27"/>
-        <v>2.0833333333333381E-4</v>
-      </c>
-      <c r="AO22" s="68">
-        <v>3</v>
-      </c>
-      <c r="AP22" s="92">
-        <v>3.7384259259259263E-3</v>
-      </c>
-      <c r="AQ22" s="69">
-        <f t="shared" si="28"/>
-        <v>9.2592592592593333E-5</v>
-      </c>
-      <c r="AR22" s="68"/>
-      <c r="AS22" s="68"/>
-      <c r="AT22" s="69" t="str">
-        <f t="shared" si="29"/>
-        <v>NA</v>
-      </c>
-      <c r="AU22" s="68"/>
-      <c r="AV22" s="68"/>
-      <c r="AW22" s="69" t="str">
-        <f t="shared" si="30"/>
-        <v>NA</v>
-      </c>
-      <c r="AX22" s="68"/>
-      <c r="AY22" s="68"/>
-      <c r="AZ22" s="69" t="str">
-        <f t="shared" si="5"/>
-        <v>NA</v>
-      </c>
-      <c r="BA22" s="68">
+        <v>NA</v>
+      </c>
+      <c r="DO22" s="33">
         <v>1</v>
       </c>
-      <c r="BB22" s="92">
-        <v>1.7361111111111112E-2</v>
-      </c>
-      <c r="BC22" s="69">
-        <f t="shared" si="31"/>
-        <v>1.3715277777777779E-2</v>
-      </c>
-      <c r="BD22" s="68"/>
-      <c r="BE22" s="68"/>
-      <c r="BF22" s="69" t="str">
-        <f t="shared" si="32"/>
-        <v>NA</v>
-      </c>
-      <c r="BG22" s="68"/>
-      <c r="BH22" s="68"/>
-      <c r="BI22" s="69" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
-      <c r="BJ22" s="68">
-        <v>1</v>
-      </c>
-      <c r="BK22" s="92">
-        <v>2.732638888888889E-2</v>
-      </c>
-      <c r="BL22" s="69">
-        <f t="shared" si="34"/>
-        <v>2.3680555555555555E-2</v>
-      </c>
-      <c r="BM22" s="68"/>
-      <c r="BN22" s="68"/>
-      <c r="BO22" s="69" t="str">
-        <f t="shared" si="35"/>
-        <v>NA</v>
-      </c>
-      <c r="BP22" s="68"/>
-      <c r="BQ22" s="68"/>
-      <c r="BR22" s="69" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="BS22" s="68"/>
-      <c r="BT22" s="68"/>
-      <c r="BU22" s="69" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="BV22" s="68"/>
-      <c r="BW22" s="68"/>
-      <c r="BX22" s="69" t="str">
-        <f t="shared" si="13"/>
-        <v>NA</v>
-      </c>
-      <c r="BY22" s="87"/>
-      <c r="BZ22" s="68"/>
-      <c r="CA22" s="69" t="str">
-        <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB22" s="68"/>
-      <c r="CC22" s="68"/>
-      <c r="CD22" s="69" t="str">
-        <f t="shared" si="15"/>
-        <v>NA</v>
-      </c>
-      <c r="CE22" s="68"/>
-      <c r="CF22" s="68"/>
-      <c r="CG22" s="69" t="str">
-        <f t="shared" si="16"/>
-        <v>NA</v>
-      </c>
-      <c r="CH22" s="68"/>
-      <c r="CI22" s="68"/>
-      <c r="CJ22" s="69" t="str">
-        <f t="shared" si="17"/>
-        <v>NA</v>
-      </c>
-      <c r="CK22" s="68"/>
-      <c r="CL22" s="68"/>
-      <c r="CM22" s="69" t="str">
-        <f t="shared" si="18"/>
-        <v>NA</v>
-      </c>
-      <c r="CN22" s="68"/>
-      <c r="CO22" s="68"/>
-      <c r="CP22" s="69" t="str">
-        <f t="shared" si="19"/>
-        <v>NA</v>
-      </c>
-      <c r="CQ22" s="68"/>
-      <c r="CR22" s="68"/>
-      <c r="CS22" s="69" t="str">
-        <f t="shared" si="20"/>
-        <v>NA</v>
-      </c>
-      <c r="CT22" s="68">
-        <v>1</v>
-      </c>
-      <c r="CU22" s="92">
-        <v>7.789351851851852E-3</v>
-      </c>
-      <c r="CV22" s="69">
-        <f t="shared" si="21"/>
-        <v>4.1435185185185186E-3</v>
-      </c>
-      <c r="CW22" s="68"/>
-      <c r="CX22" s="92"/>
-      <c r="CY22" s="69" t="str">
-        <f t="shared" si="22"/>
-        <v>NA</v>
-      </c>
-      <c r="CZ22" s="68">
-        <v>2</v>
-      </c>
-      <c r="DA22" s="92">
-        <v>2.3541666666666666E-2</v>
-      </c>
-      <c r="DB22" s="69">
-        <f t="shared" si="38"/>
-        <v>1.9895833333333331E-2</v>
-      </c>
-      <c r="DC22" s="68"/>
+      <c r="DP22" s="35">
+        <v>1.8900462962962963E-2</v>
+      </c>
+      <c r="DQ22" s="64">
+        <f t="shared" si="43"/>
+        <v>1.525462962962963E-2</v>
+      </c>
+      <c r="DR22" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7055,7 +7881,7 @@
       <c r="C2" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="63">
+      <c r="D2" s="62">
         <v>0.35000000000000003</v>
       </c>
       <c r="E2" t="s">
@@ -7072,7 +7898,7 @@
       <c r="C3" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="63">
+      <c r="D3" s="62">
         <v>0.59236111111111112</v>
       </c>
     </row>
@@ -7086,7 +7912,7 @@
       <c r="C4" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="63">
+      <c r="D4" s="62">
         <v>0.59513888888888888</v>
       </c>
     </row>
@@ -7243,108 +8069,108 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:36" s="62" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="45" t="s">
+    <row r="2" spans="1:36" s="61" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="49" t="s">
+      <c r="F2" s="46"/>
+      <c r="G2" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="J2" s="50" t="s">
+      <c r="J2" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="L2" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="M2" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="O2" s="49" t="s">
+      <c r="O2" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="47" t="s">
+      <c r="P2" s="48"/>
+      <c r="Q2" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="R2" s="47" t="s">
+      <c r="R2" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="S2" s="47" t="s">
+      <c r="S2" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="T2" s="51"/>
-      <c r="U2" s="52" t="s">
+      <c r="T2" s="50"/>
+      <c r="U2" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="V2" s="52" t="s">
+      <c r="V2" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="W2" s="52" t="s">
+      <c r="W2" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="X2" s="53">
+      <c r="X2" s="52">
         <f>SUM(U2:W2)</f>
         <v>0</v>
       </c>
-      <c r="Y2" s="53" t="s">
+      <c r="Y2" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="Z2" s="53" t="s">
+      <c r="Z2" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="AA2" s="53" t="e">
+      <c r="AA2" s="52" t="e">
         <f>X2-Y2-Z2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB2" s="54" t="s">
+      <c r="AB2" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="AC2" s="54" t="s">
+      <c r="AC2" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="56" t="s">
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="AF2" s="57" t="s">
+      <c r="AF2" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="AG2" s="58" t="s">
+      <c r="AG2" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="AH2" s="59" t="s">
+      <c r="AH2" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="AI2" s="60" t="e">
+      <c r="AI2" s="59" t="e">
         <f>IF(AG2=0,"NA",AH2-$Y2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AJ2" s="61"/>
+      <c r="AJ2" s="60"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3" s="9"/>
@@ -8078,7 +8904,7 @@
       <c r="AF20" s="39"/>
       <c r="AG20" s="40"/>
       <c r="AH20" s="42"/>
-      <c r="AI20" s="44" t="str">
+      <c r="AI20" s="43" t="str">
         <f t="shared" si="2"/>
         <v>NA</v>
       </c>
@@ -8096,236 +8922,236 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="68" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="70" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="77">
+      <c r="B2" s="72">
         <v>-5.4793240000000001</v>
       </c>
-      <c r="C2" s="77">
+      <c r="C2" s="72">
         <v>119.31157399999999</v>
       </c>
-      <c r="D2" s="78"/>
+      <c r="D2" s="73"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="77">
+      <c r="B3" s="72">
         <v>-5.4880659999999999</v>
       </c>
-      <c r="C3" s="77">
+      <c r="C3" s="72">
         <v>119.31312699999999</v>
       </c>
-      <c r="D3" s="78"/>
+      <c r="D3" s="73"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="71" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="77">
+      <c r="B4" s="72">
         <v>-5.4889159999999997</v>
       </c>
-      <c r="C4" s="77">
+      <c r="C4" s="72">
         <v>119.309448</v>
       </c>
-      <c r="D4" s="78" t="s">
+      <c r="D4" s="73" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="B5" s="77">
+      <c r="B5" s="72">
         <v>-5.468826</v>
       </c>
-      <c r="C5" s="77">
+      <c r="C5" s="72">
         <v>119.300459</v>
       </c>
-      <c r="D5" s="78"/>
+      <c r="D5" s="73"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="77">
+      <c r="B6" s="72">
         <v>-5.4682649999999997</v>
       </c>
-      <c r="C6" s="77">
+      <c r="C6" s="72">
         <v>119.30207900000001</v>
       </c>
-      <c r="D6" s="78"/>
+      <c r="D6" s="73"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="71" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="77">
+      <c r="B7" s="72">
         <v>-5.4671349999999999</v>
       </c>
-      <c r="C7" s="77">
+      <c r="C7" s="72">
         <v>119.302812</v>
       </c>
-      <c r="D7" s="78"/>
+      <c r="D7" s="73"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="77">
+      <c r="B8" s="72">
         <v>-5.4901910000000003</v>
       </c>
-      <c r="C8" s="77">
+      <c r="C8" s="72">
         <v>119.311859</v>
       </c>
-      <c r="D8" s="78"/>
+      <c r="D8" s="73"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="71" t="s">
         <v>160</v>
       </c>
-      <c r="B9" s="77">
+      <c r="B9" s="72">
         <v>-5.491987</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="72">
         <v>119.312573</v>
       </c>
-      <c r="D9" s="78"/>
+      <c r="D9" s="73"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="B10" s="77">
+      <c r="B10" s="72">
         <v>-5.49282</v>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="72">
         <v>119.31198000000001</v>
       </c>
-      <c r="D10" s="78"/>
+      <c r="D10" s="73"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="B11" s="77">
+      <c r="B11" s="72">
         <v>-5.4639509999999998</v>
       </c>
-      <c r="C11" s="77">
+      <c r="C11" s="72">
         <v>119.287291</v>
       </c>
-      <c r="D11" s="78"/>
+      <c r="D11" s="73"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="77">
+      <c r="B12" s="72">
         <v>-5.4620889999999997</v>
       </c>
-      <c r="C12" s="77">
+      <c r="C12" s="72">
         <v>119.286874</v>
       </c>
-      <c r="D12" s="78"/>
+      <c r="D12" s="73"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="71" t="s">
         <v>163</v>
       </c>
-      <c r="B13" s="77">
+      <c r="B13" s="72">
         <v>-5.463902</v>
       </c>
-      <c r="C13" s="77">
+      <c r="C13" s="72">
         <v>119.28802</v>
       </c>
-      <c r="D13" s="78"/>
+      <c r="D13" s="73"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="71" t="s">
         <v>164</v>
       </c>
-      <c r="B14" s="77">
+      <c r="B14" s="72">
         <v>-5.4810160000000003</v>
       </c>
-      <c r="C14" s="77">
+      <c r="C14" s="72">
         <v>119.31128099999999</v>
       </c>
-      <c r="D14" s="78"/>
+      <c r="D14" s="73"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="76" t="s">
+      <c r="A15" s="71" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="77">
+      <c r="B15" s="72">
         <v>-5.4811319999999997</v>
       </c>
-      <c r="C15" s="77">
+      <c r="C15" s="72">
         <v>119.31211</v>
       </c>
-      <c r="D15" s="78"/>
+      <c r="D15" s="73"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="71" t="s">
         <v>166</v>
       </c>
-      <c r="B16" s="77">
+      <c r="B16" s="72">
         <v>-5.4793599999999998</v>
       </c>
-      <c r="C16" s="77">
+      <c r="C16" s="72">
         <v>119.312033</v>
       </c>
-      <c r="D16" s="78"/>
+      <c r="D16" s="73"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="76" t="s">
+      <c r="A17" s="71" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="77">
+      <c r="B17" s="72">
         <v>-5.4663769999999996</v>
       </c>
-      <c r="C17" s="77">
+      <c r="C17" s="72">
         <v>119.30229</v>
       </c>
-      <c r="D17" s="78"/>
+      <c r="D17" s="73"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="76" t="s">
+      <c r="A18" s="71" t="s">
         <v>168</v>
       </c>
-      <c r="B18" s="77">
+      <c r="B18" s="72">
         <v>-5.4682510000000004</v>
       </c>
-      <c r="C18" s="77">
+      <c r="C18" s="72">
         <v>119.301957</v>
       </c>
-      <c r="D18" s="78"/>
+      <c r="D18" s="73"/>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="79" t="s">
+      <c r="A19" s="74" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="80">
+      <c r="B19" s="75">
         <v>-5.4686510000000004</v>
       </c>
-      <c r="C19" s="80">
+      <c r="C19" s="75">
         <v>119.300428</v>
       </c>
-      <c r="D19" s="81"/>
+      <c r="D19" s="76"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/URUVS/Datasheets/URUV/03.2024/March_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/03.2024/March_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\03.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1427E9E4-8EE6-4AC8-B23E-A89F7326A867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3B9D0F-6C8F-4EB8-BBE5-A842E3B2D9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -4075,10 +4075,10 @@
       </c>
       <c r="AI10" s="22"/>
       <c r="AJ10" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK10" s="31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL10" s="32">
         <v>1</v>
@@ -4236,11 +4236,15 @@
         <f t="shared" si="24"/>
         <v>2.1990740740740738E-3</v>
       </c>
-      <c r="DF10" s="32"/>
-      <c r="DG10" s="35"/>
-      <c r="DH10" s="34" t="str">
+      <c r="DF10" s="32">
+        <v>2</v>
+      </c>
+      <c r="DG10" s="35">
+        <v>6.5509259259259262E-3</v>
+      </c>
+      <c r="DH10" s="34">
         <f t="shared" si="25"/>
-        <v>NA</v>
+        <v>1.9097222222222224E-3</v>
       </c>
       <c r="DI10" s="32"/>
       <c r="DJ10" s="35"/>

--- a/URUVS/Datasheets/URUV/03.2024/March_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/03.2024/March_RecordingData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\03.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3B9D0F-6C8F-4EB8-BBE5-A842E3B2D9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF46E3CE-9061-4D30-BB55-3099120B72CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -653,9 +653,6 @@
     <t>T1_SANDFISH</t>
   </si>
   <si>
-    <t>MAXN_FISHCHEETAGIRLZ</t>
-  </si>
-  <si>
     <t>TIME_1STCHEETAGIRLZ</t>
   </si>
   <si>
@@ -711,6 +708,9 @@
   </si>
   <si>
     <t>T1_ULAR</t>
+  </si>
+  <si>
+    <t>MAXN_CHEETAGIRLZ</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1379,7 @@
   <sheetData>
     <row r="1" spans="1:122" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1625,22 +1625,22 @@
         <v>195</v>
       </c>
       <c r="CE1" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="CF1" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="CF1" s="28" t="s">
+      <c r="CG1" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="CG1" s="67" t="s">
-        <v>217</v>
-      </c>
       <c r="CH1" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI1" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="CI1" s="28" t="s">
+      <c r="CJ1" s="67" t="s">
         <v>205</v>
-      </c>
-      <c r="CJ1" s="67" t="s">
-        <v>206</v>
       </c>
       <c r="CK1" s="27" t="s">
         <v>178</v>
@@ -1706,40 +1706,40 @@
         <v>33</v>
       </c>
       <c r="DF1" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="DG1" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="DG1" s="28" t="s">
+      <c r="DH1" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="DH1" s="67" t="s">
+      <c r="DI1" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="DI1" s="27" t="s">
+      <c r="DJ1" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="DJ1" s="28" t="s">
+      <c r="DK1" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="DK1" s="67" t="s">
-        <v>214</v>
-      </c>
       <c r="DL1" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="DM1" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="DM1" s="28" t="s">
+      <c r="DN1" s="67" t="s">
         <v>219</v>
       </c>
-      <c r="DN1" s="67" t="s">
+      <c r="DO1" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="DO1" s="27" t="s">
+      <c r="DP1" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="DP1" s="28" t="s">
+      <c r="DQ1" s="67" t="s">
         <v>222</v>
-      </c>
-      <c r="DQ1" s="67" t="s">
-        <v>223</v>
       </c>
       <c r="DR1" s="29" t="s">
         <v>31</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="2" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>93</v>
@@ -1797,7 +1797,10 @@
       <c r="P2" s="5">
         <v>3</v>
       </c>
-      <c r="Q2" s="6"/>
+      <c r="Q2" s="6" t="e">
+        <f>J2-I2</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="R2" s="6" t="s">
         <v>100</v>
       </c>
@@ -2040,7 +2043,7 @@
     </row>
     <row r="3" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>93</v>
@@ -2088,7 +2091,10 @@
       <c r="P3" s="5">
         <v>6</v>
       </c>
-      <c r="Q3" s="6"/>
+      <c r="Q3" s="6" t="e">
+        <f t="shared" ref="Q3:Q22" si="30">J3-I3</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="R3" s="6" t="s">
         <v>102</v>
       </c>
@@ -2123,7 +2129,7 @@
         <v>1.1342592592592591E-3</v>
       </c>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC22" si="30">SUM(W3:AB3)</f>
+        <f t="shared" ref="AC3:AC22" si="31">SUM(W3:AB3)</f>
         <v>7.8148148148148147E-2</v>
       </c>
       <c r="AD3" s="20">
@@ -2321,7 +2327,7 @@
     </row>
     <row r="4" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>93</v>
@@ -2371,7 +2377,10 @@
       <c r="P4" s="5">
         <v>3</v>
       </c>
-      <c r="Q4" s="6"/>
+      <c r="Q4" s="6">
+        <f t="shared" si="30"/>
+        <v>7.7083333333333393E-2</v>
+      </c>
       <c r="R4" s="6" t="s">
         <v>107</v>
       </c>
@@ -2398,7 +2407,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6.0902777777777778E-2</v>
       </c>
       <c r="AD4" s="20">
@@ -2620,7 +2629,7 @@
     </row>
     <row r="5" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>93</v>
@@ -2670,7 +2679,10 @@
       <c r="P5" s="5">
         <v>3</v>
       </c>
-      <c r="Q5" s="6"/>
+      <c r="Q5" s="6">
+        <f t="shared" si="30"/>
+        <v>6.944444444444442E-2</v>
+      </c>
       <c r="R5" s="6" t="s">
         <v>108</v>
       </c>
@@ -2693,7 +2705,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AD5" s="20"/>
@@ -2879,7 +2891,7 @@
     </row>
     <row r="6" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>93</v>
@@ -2929,7 +2941,10 @@
       <c r="P6" s="5">
         <v>3</v>
       </c>
-      <c r="Q6" s="6"/>
+      <c r="Q6" s="6">
+        <f t="shared" si="30"/>
+        <v>6.25E-2</v>
+      </c>
       <c r="R6" s="6" t="s">
         <v>109</v>
       </c>
@@ -2952,7 +2967,7 @@
       <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AD6" s="20"/>
@@ -3138,7 +3153,7 @@
     </row>
     <row r="7" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>93</v>
@@ -3188,7 +3203,10 @@
       <c r="P7" s="5">
         <v>3</v>
       </c>
-      <c r="Q7" s="6"/>
+      <c r="Q7" s="6">
+        <f t="shared" si="30"/>
+        <v>5.0694444444444375E-2</v>
+      </c>
       <c r="R7" s="6" t="s">
         <v>110</v>
       </c>
@@ -3211,7 +3229,7 @@
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AD7" s="20"/>
@@ -3397,7 +3415,7 @@
     </row>
     <row r="8" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>120</v>
@@ -3447,7 +3465,10 @@
       <c r="P8" s="5">
         <v>2</v>
       </c>
-      <c r="Q8" s="6"/>
+      <c r="Q8" s="6">
+        <f t="shared" si="30"/>
+        <v>5.1388888888888928E-2</v>
+      </c>
       <c r="R8" s="6" t="s">
         <v>125</v>
       </c>
@@ -3474,7 +3495,7 @@
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.3020833333333336E-2</v>
       </c>
       <c r="AD8" s="20">
@@ -3684,7 +3705,7 @@
     </row>
     <row r="9" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>120</v>
@@ -3734,7 +3755,10 @@
       <c r="P9" s="5">
         <v>3</v>
       </c>
-      <c r="Q9" s="6"/>
+      <c r="Q9" s="6">
+        <f t="shared" si="30"/>
+        <v>5.3472222222222254E-2</v>
+      </c>
       <c r="R9" s="6" t="s">
         <v>121</v>
       </c>
@@ -3763,7 +3787,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4.5902777777777778E-2</v>
       </c>
       <c r="AD9" s="20">
@@ -3971,7 +3995,7 @@
     </row>
     <row r="10" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>120</v>
@@ -4021,7 +4045,10 @@
       <c r="P10" s="5">
         <v>5</v>
       </c>
-      <c r="Q10" s="6"/>
+      <c r="Q10" s="6">
+        <f t="shared" si="30"/>
+        <v>5.1388888888888928E-2</v>
+      </c>
       <c r="R10" s="6" t="s">
         <v>102</v>
       </c>
@@ -4054,7 +4081,7 @@
       </c>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.2268518518518513E-2</v>
       </c>
       <c r="AD10" s="20">
@@ -4268,7 +4295,7 @@
     </row>
     <row r="11" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>120</v>
@@ -4318,7 +4345,10 @@
       <c r="P11" s="5">
         <v>2</v>
       </c>
-      <c r="Q11" s="6"/>
+      <c r="Q11" s="6">
+        <f t="shared" si="30"/>
+        <v>5.2083333333333259E-2</v>
+      </c>
       <c r="R11" s="6" t="s">
         <v>122</v>
       </c>
@@ -4343,7 +4373,7 @@
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.1307870370370365E-2</v>
       </c>
       <c r="AD11" s="20">
@@ -4593,7 +4623,7 @@
     </row>
     <row r="12" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>120</v>
@@ -4643,7 +4673,10 @@
       <c r="P12" s="5">
         <v>3</v>
       </c>
-      <c r="Q12" s="6"/>
+      <c r="Q12" s="6">
+        <f t="shared" si="30"/>
+        <v>4.9305555555555491E-2</v>
+      </c>
       <c r="R12" s="6" t="s">
         <v>123</v>
       </c>
@@ -4670,7 +4703,7 @@
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4.9548611111111106E-2</v>
       </c>
       <c r="AD12" s="20">
@@ -4876,7 +4909,7 @@
     </row>
     <row r="13" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>120</v>
@@ -4926,7 +4959,10 @@
       <c r="P13" s="5">
         <v>2</v>
       </c>
-      <c r="Q13" s="6"/>
+      <c r="Q13" s="6">
+        <f t="shared" si="30"/>
+        <v>5.3472222222222254E-2</v>
+      </c>
       <c r="R13" s="6" t="s">
         <v>124</v>
       </c>
@@ -4951,7 +4987,7 @@
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.5509259259259258E-2</v>
       </c>
       <c r="AD13" s="20">
@@ -5173,7 +5209,7 @@
     </row>
     <row r="14" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>132</v>
@@ -5223,7 +5259,10 @@
       <c r="P14" s="5">
         <v>4</v>
       </c>
-      <c r="Q14" s="6"/>
+      <c r="Q14" s="6">
+        <f t="shared" si="30"/>
+        <v>7.4999999999999956E-2</v>
+      </c>
       <c r="R14" s="6" t="s">
         <v>133</v>
       </c>
@@ -5252,7 +5291,7 @@
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6.1759259259259257E-2</v>
       </c>
       <c r="AD14" s="20">
@@ -5262,7 +5301,7 @@
         <v>1.5127314814814816E-2</v>
       </c>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF22" si="31">AC14-AD14-AE14</f>
+        <f t="shared" ref="AF14:AF22" si="32">AC14-AD14-AE14</f>
         <v>4.2905092592592592E-2</v>
       </c>
       <c r="AG14" s="21">
@@ -5281,25 +5320,25 @@
       <c r="AL14" s="32"/>
       <c r="AM14" s="33"/>
       <c r="AN14" s="34" t="str">
-        <f t="shared" ref="AN14:AN22" si="32">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN22" si="33">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AO14" s="32"/>
       <c r="AP14" s="33"/>
       <c r="AQ14" s="34" t="str">
-        <f t="shared" ref="AQ14:AQ22" si="33">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ22" si="34">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AR14" s="32"/>
       <c r="AS14" s="33"/>
       <c r="AT14" s="34" t="str">
-        <f t="shared" ref="AT14:AT22" si="34">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT22" si="35">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AU14" s="33"/>
       <c r="AV14" s="33"/>
       <c r="AW14" s="34" t="str">
-        <f t="shared" ref="AW14:AW22" si="35">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW22" si="36">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="32"/>
@@ -5311,19 +5350,19 @@
       <c r="BA14" s="32"/>
       <c r="BB14" s="35"/>
       <c r="BC14" s="34" t="str">
-        <f t="shared" ref="BC14:BC22" si="36">IF(BA14=0,"NA",BB14-$AD14)</f>
+        <f t="shared" ref="BC14:BC22" si="37">IF(BA14=0,"NA",BB14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BD14" s="32"/>
       <c r="BE14" s="33"/>
       <c r="BF14" s="34" t="str">
-        <f t="shared" ref="BF14:BF22" si="37">IF(BD14=0,"NA",BE14-$AD14)</f>
+        <f t="shared" ref="BF14:BF22" si="38">IF(BD14=0,"NA",BE14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BG14" s="32"/>
       <c r="BH14" s="35"/>
       <c r="BI14" s="34" t="str">
-        <f t="shared" ref="BI14:BI22" si="38">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI22" si="39">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="32">
@@ -5333,19 +5372,19 @@
         <v>1.8148148148148146E-2</v>
       </c>
       <c r="BL14" s="34">
-        <f t="shared" ref="BL14:BL22" si="39">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <f t="shared" ref="BL14:BL22" si="40">IF(BJ14=0,"NA",BK14-$AD14)</f>
         <v>1.4421296296296295E-2</v>
       </c>
       <c r="BM14" s="33"/>
       <c r="BN14" s="33"/>
       <c r="BO14" s="34" t="str">
-        <f t="shared" ref="BO14:BO22" si="40">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <f t="shared" ref="BO14:BO22" si="41">IF(BM14=0,"NA",BN14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BP14" s="32"/>
       <c r="BQ14" s="33"/>
       <c r="BR14" s="34" t="str">
-        <f t="shared" ref="BR14:BR22" si="41">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR22" si="42">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="32">
@@ -5355,7 +5394,7 @@
         <v>1.653935185185185E-2</v>
       </c>
       <c r="BU14" s="34">
-        <f t="shared" ref="BU14:BU22" si="42">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <f t="shared" ref="BU14:BU22" si="43">IF(BS14=0,"NA",BT14-$AD14)</f>
         <v>1.2812499999999999E-2</v>
       </c>
       <c r="BV14" s="32"/>
@@ -5463,14 +5502,14 @@
       <c r="DO14" s="32"/>
       <c r="DP14" s="35"/>
       <c r="DQ14" s="34" t="str">
-        <f t="shared" ref="DQ14:DQ22" si="43">IF(DO14=0,"NA",DP14-$AD14)</f>
+        <f t="shared" ref="DQ14:DQ22" si="44">IF(DO14=0,"NA",DP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="DR14" s="37"/>
     </row>
     <row r="15" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>132</v>
@@ -5520,7 +5559,10 @@
       <c r="P15" s="5">
         <v>3</v>
       </c>
-      <c r="Q15" s="6"/>
+      <c r="Q15" s="6">
+        <f t="shared" si="30"/>
+        <v>6.944444444444442E-2</v>
+      </c>
       <c r="R15" s="6" t="s">
         <v>124</v>
       </c>
@@ -5547,7 +5589,7 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.0416666666666665E-2</v>
       </c>
       <c r="AD15" s="20">
@@ -5555,7 +5597,7 @@
       </c>
       <c r="AE15" s="20"/>
       <c r="AF15" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.4537037037037035E-2</v>
       </c>
       <c r="AG15" s="21">
@@ -5578,25 +5620,25 @@
         <v>1.3333333333333334E-2</v>
       </c>
       <c r="AN15" s="34">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.4537037037037046E-3</v>
       </c>
       <c r="AO15" s="32"/>
       <c r="AP15" s="33"/>
       <c r="AQ15" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR15" s="32"/>
       <c r="AS15" s="33"/>
       <c r="AT15" s="34" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU15" s="33"/>
       <c r="AV15" s="33"/>
       <c r="AW15" s="34" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="32"/>
@@ -5608,37 +5650,37 @@
       <c r="BA15" s="32"/>
       <c r="BB15" s="33"/>
       <c r="BC15" s="34" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BD15" s="32"/>
       <c r="BE15" s="33"/>
       <c r="BF15" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG15" s="32"/>
       <c r="BH15" s="35"/>
       <c r="BI15" s="34" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="32"/>
       <c r="BK15" s="33"/>
       <c r="BL15" s="34" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM15" s="32"/>
       <c r="BN15" s="33"/>
       <c r="BO15" s="34" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BP15" s="32"/>
       <c r="BQ15" s="33"/>
       <c r="BR15" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS15" s="32">
@@ -5648,7 +5690,7 @@
         <v>7.9976851851851858E-3</v>
       </c>
       <c r="BU15" s="34">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.1180555555555562E-3</v>
       </c>
       <c r="BV15" s="32">
@@ -5760,14 +5802,14 @@
       <c r="DO15" s="32"/>
       <c r="DP15" s="33"/>
       <c r="DQ15" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="DR15" s="37"/>
     </row>
     <row r="16" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>132</v>
@@ -5817,7 +5859,10 @@
       <c r="P16" s="5">
         <v>4</v>
       </c>
-      <c r="Q16" s="6"/>
+      <c r="Q16" s="6">
+        <f t="shared" si="30"/>
+        <v>4.7222222222222221E-2</v>
+      </c>
       <c r="R16" s="6" t="s">
         <v>100</v>
       </c>
@@ -5846,7 +5891,7 @@
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
       <c r="AC16" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4.7905092592592589E-2</v>
       </c>
       <c r="AD16" s="20">
@@ -5856,7 +5901,7 @@
         <v>1.3888888888888889E-3</v>
       </c>
       <c r="AF16" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.1932870370370363E-2</v>
       </c>
       <c r="AG16" s="21">
@@ -5875,13 +5920,13 @@
       <c r="AL16" s="32"/>
       <c r="AM16" s="35"/>
       <c r="AN16" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO16" s="32"/>
       <c r="AP16" s="35"/>
       <c r="AQ16" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR16" s="32">
@@ -5891,13 +5936,13 @@
         <v>3.0555555555555555E-2</v>
       </c>
       <c r="AT16" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2.5972222222222223E-2</v>
       </c>
       <c r="AU16" s="32"/>
       <c r="AV16" s="35"/>
       <c r="AW16" s="34" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="32"/>
@@ -5909,19 +5954,19 @@
       <c r="BA16" s="32"/>
       <c r="BB16" s="35"/>
       <c r="BC16" s="34" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BD16" s="32"/>
       <c r="BE16" s="35"/>
       <c r="BF16" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG16" s="32"/>
       <c r="BH16" s="35"/>
       <c r="BI16" s="34" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ16" s="32">
@@ -5931,19 +5976,19 @@
         <v>5.7407407407407416E-3</v>
       </c>
       <c r="BL16" s="34">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.1574074074074082E-3</v>
       </c>
       <c r="BM16" s="32"/>
       <c r="BN16" s="33"/>
       <c r="BO16" s="34" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BP16" s="32"/>
       <c r="BQ16" s="33"/>
       <c r="BR16" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="32">
@@ -5953,7 +5998,7 @@
         <v>3.1041666666666665E-2</v>
       </c>
       <c r="BU16" s="34">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.6458333333333334E-2</v>
       </c>
       <c r="BV16" s="32"/>
@@ -6057,14 +6102,14 @@
       <c r="DO16" s="32"/>
       <c r="DP16" s="35"/>
       <c r="DQ16" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="DR16" s="37"/>
     </row>
     <row r="17" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>132</v>
@@ -6114,7 +6159,10 @@
       <c r="P17" s="5">
         <v>2</v>
       </c>
-      <c r="Q17" s="6"/>
+      <c r="Q17" s="6">
+        <f t="shared" si="30"/>
+        <v>8.6111111111111138E-2</v>
+      </c>
       <c r="R17" s="6" t="s">
         <v>107</v>
       </c>
@@ -6139,7 +6187,7 @@
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.7766203703703708E-2</v>
       </c>
       <c r="AD17" s="20">
@@ -6149,7 +6197,7 @@
         <v>7.9861111111111122E-3</v>
       </c>
       <c r="AF17" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.2488425925925929E-2</v>
       </c>
       <c r="AG17" s="21">
@@ -6168,7 +6216,7 @@
       <c r="AL17" s="32"/>
       <c r="AM17" s="35"/>
       <c r="AN17" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO17" s="32">
@@ -6178,7 +6226,7 @@
         <v>4.2083333333333334E-2</v>
       </c>
       <c r="AQ17" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3.4791666666666665E-2</v>
       </c>
       <c r="AR17" s="32">
@@ -6188,13 +6236,13 @@
         <v>2.5196759259259256E-2</v>
       </c>
       <c r="AT17" s="34">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1.7905092592592591E-2</v>
       </c>
       <c r="AU17" s="32"/>
       <c r="AV17" s="35"/>
       <c r="AW17" s="34" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="32"/>
@@ -6210,43 +6258,43 @@
         <v>3.3854166666666664E-2</v>
       </c>
       <c r="BC17" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2.6562499999999999E-2</v>
       </c>
       <c r="BD17" s="32"/>
       <c r="BE17" s="35"/>
       <c r="BF17" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG17" s="32"/>
       <c r="BH17" s="35"/>
       <c r="BI17" s="34" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ17" s="32"/>
       <c r="BK17" s="35"/>
       <c r="BL17" s="34" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM17" s="32"/>
       <c r="BN17" s="35"/>
       <c r="BO17" s="34" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BP17" s="32"/>
       <c r="BQ17" s="35"/>
       <c r="BR17" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS17" s="32"/>
       <c r="BT17" s="33"/>
       <c r="BU17" s="34" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BV17" s="32"/>
@@ -6350,14 +6398,14 @@
       <c r="DO17" s="32"/>
       <c r="DP17" s="35"/>
       <c r="DQ17" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="DR17" s="37"/>
     </row>
     <row r="18" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>132</v>
@@ -6407,7 +6455,10 @@
       <c r="P18" s="5">
         <v>3</v>
       </c>
-      <c r="Q18" s="6"/>
+      <c r="Q18" s="6">
+        <f t="shared" si="30"/>
+        <v>8.1944444444444375E-2</v>
+      </c>
       <c r="R18" s="6" t="s">
         <v>125</v>
       </c>
@@ -6434,7 +6485,7 @@
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.6296296296296289E-2</v>
       </c>
       <c r="AD18" s="20">
@@ -6444,7 +6495,7 @@
         <v>9.2361111111111116E-3</v>
       </c>
       <c r="AF18" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.2905092592592585E-2</v>
       </c>
       <c r="AG18" s="21">
@@ -6463,7 +6514,7 @@
       <c r="AL18" s="32"/>
       <c r="AM18" s="35"/>
       <c r="AN18" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO18" s="32">
@@ -6473,19 +6524,19 @@
         <v>2.3078703703703702E-2</v>
       </c>
       <c r="AQ18" s="34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.892361111111111E-2</v>
       </c>
       <c r="AR18" s="32"/>
       <c r="AS18" s="35"/>
       <c r="AT18" s="34" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU18" s="32"/>
       <c r="AV18" s="35"/>
       <c r="AW18" s="34" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX18" s="32"/>
@@ -6501,43 +6552,43 @@
         <v>1.3321759259259261E-2</v>
       </c>
       <c r="BC18" s="34">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9.1666666666666667E-3</v>
       </c>
       <c r="BD18" s="32"/>
       <c r="BE18" s="35"/>
       <c r="BF18" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG18" s="32"/>
       <c r="BH18" s="35"/>
       <c r="BI18" s="34" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="32"/>
       <c r="BK18" s="35"/>
       <c r="BL18" s="34" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM18" s="32"/>
       <c r="BN18" s="35"/>
       <c r="BO18" s="34" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BP18" s="32"/>
       <c r="BQ18" s="35"/>
       <c r="BR18" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="32"/>
       <c r="BT18" s="33"/>
       <c r="BU18" s="34" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BV18" s="32"/>
@@ -6637,14 +6688,14 @@
       <c r="DO18" s="32"/>
       <c r="DP18" s="35"/>
       <c r="DQ18" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="DR18" s="37"/>
     </row>
     <row r="19" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>132</v>
@@ -6694,7 +6745,10 @@
       <c r="P19" s="5">
         <v>4</v>
       </c>
-      <c r="Q19" s="6"/>
+      <c r="Q19" s="6">
+        <f t="shared" si="30"/>
+        <v>7.1527777777777746E-2</v>
+      </c>
       <c r="R19" s="6" t="s">
         <v>108</v>
       </c>
@@ -6721,7 +6775,7 @@
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.2766203703703704E-2</v>
       </c>
       <c r="AD19" s="20">
@@ -6729,7 +6783,7 @@
       </c>
       <c r="AE19" s="20"/>
       <c r="AF19" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>3.5868055555555556E-2</v>
       </c>
       <c r="AG19" s="21">
@@ -6748,7 +6802,7 @@
       <c r="AL19" s="33"/>
       <c r="AM19" s="35"/>
       <c r="AN19" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO19" s="33">
@@ -6758,19 +6812,19 @@
         <v>1.2</v>
       </c>
       <c r="AQ19" s="64">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.1831018518518519</v>
       </c>
       <c r="AR19" s="33"/>
       <c r="AS19" s="35"/>
       <c r="AT19" s="64" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU19" s="33"/>
       <c r="AV19" s="35"/>
       <c r="AW19" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX19" s="33"/>
@@ -6786,43 +6840,43 @@
         <v>2.2754629629629628E-2</v>
       </c>
       <c r="BC19" s="64">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.8564814814814799E-3</v>
       </c>
       <c r="BD19" s="33"/>
       <c r="BE19" s="35"/>
       <c r="BF19" s="64" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG19" s="33"/>
       <c r="BH19" s="35"/>
       <c r="BI19" s="64" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="33"/>
       <c r="BK19" s="35"/>
       <c r="BL19" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM19" s="33"/>
       <c r="BN19" s="35"/>
       <c r="BO19" s="64" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BP19" s="33"/>
       <c r="BQ19" s="35"/>
       <c r="BR19" s="64" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="33"/>
       <c r="BT19" s="33"/>
       <c r="BU19" s="64" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BV19" s="33"/>
@@ -6885,11 +6939,15 @@
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ19" s="33"/>
-      <c r="DA19" s="35"/>
-      <c r="DB19" s="64" t="str">
+      <c r="CZ19" s="33">
+        <v>1</v>
+      </c>
+      <c r="DA19" s="64">
+        <v>1.2305555555555556</v>
+      </c>
+      <c r="DB19" s="64">
         <f t="shared" si="23"/>
-        <v>NA</v>
+        <v>1.2136574074074076</v>
       </c>
       <c r="DC19" s="33">
         <v>2</v>
@@ -6930,14 +6988,14 @@
       <c r="DO19" s="33"/>
       <c r="DP19" s="35"/>
       <c r="DQ19" s="64" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="DR19" s="33"/>
     </row>
     <row r="20" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>132</v>
@@ -6987,7 +7045,10 @@
       <c r="P20" s="5">
         <v>3</v>
       </c>
-      <c r="Q20" s="6"/>
+      <c r="Q20" s="6">
+        <f t="shared" si="30"/>
+        <v>6.6666666666666652E-2</v>
+      </c>
       <c r="R20" s="6" t="s">
         <v>136</v>
       </c>
@@ -7014,7 +7075,7 @@
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6.4189814814814811E-2</v>
       </c>
       <c r="AD20" s="20">
@@ -7024,7 +7085,7 @@
         <v>1.5046296296296295E-2</v>
       </c>
       <c r="AF20" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.4687499999999998E-2</v>
       </c>
       <c r="AG20" s="21">
@@ -7043,25 +7104,25 @@
       <c r="AL20" s="33"/>
       <c r="AM20" s="35"/>
       <c r="AN20" s="64" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO20" s="33"/>
       <c r="AP20" s="35"/>
       <c r="AQ20" s="64" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR20" s="33"/>
       <c r="AS20" s="35"/>
       <c r="AT20" s="64" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU20" s="33"/>
       <c r="AV20" s="35"/>
       <c r="AW20" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX20" s="33"/>
@@ -7077,43 +7138,43 @@
         <v>3.050925925925926E-2</v>
       </c>
       <c r="BC20" s="64">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2.6053240740740741E-2</v>
       </c>
       <c r="BD20" s="33"/>
       <c r="BE20" s="35"/>
       <c r="BF20" s="64" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG20" s="33"/>
       <c r="BH20" s="35"/>
       <c r="BI20" s="64" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ20" s="33"/>
       <c r="BK20" s="35"/>
       <c r="BL20" s="64" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BM20" s="33"/>
       <c r="BN20" s="35"/>
       <c r="BO20" s="64" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BP20" s="33"/>
       <c r="BQ20" s="35"/>
       <c r="BR20" s="64" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS20" s="33"/>
       <c r="BT20" s="35"/>
       <c r="BU20" s="64" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BV20" s="33"/>
@@ -7217,14 +7278,14 @@
       <c r="DO20" s="33"/>
       <c r="DP20" s="35"/>
       <c r="DQ20" s="64" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="DR20" s="33"/>
     </row>
     <row r="21" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>132</v>
@@ -7274,7 +7335,10 @@
       <c r="P21" s="5">
         <v>3</v>
       </c>
-      <c r="Q21" s="5"/>
+      <c r="Q21" s="6">
+        <f t="shared" si="30"/>
+        <v>4.861111111111116E-2</v>
+      </c>
       <c r="R21" s="5" t="s">
         <v>123</v>
       </c>
@@ -7301,7 +7365,7 @@
       <c r="AA21" s="63"/>
       <c r="AB21" s="63"/>
       <c r="AC21" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>4.9618055555555554E-2</v>
       </c>
       <c r="AD21" s="82">
@@ -7311,7 +7375,7 @@
         <v>2.3148148148148146E-4</v>
       </c>
       <c r="AF21" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.5023148148148152E-2</v>
       </c>
       <c r="AG21" s="21">
@@ -7334,7 +7398,7 @@
         <v>2.0254629629629629E-2</v>
       </c>
       <c r="AN21" s="64">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1.5891203703703703E-2</v>
       </c>
       <c r="AO21" s="33">
@@ -7344,19 +7408,19 @@
         <v>4.9166666666666664E-2</v>
       </c>
       <c r="AQ21" s="64">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.4803240740740741E-2</v>
       </c>
       <c r="AR21" s="33"/>
       <c r="AS21" s="33"/>
       <c r="AT21" s="64" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU21" s="33"/>
       <c r="AV21" s="33"/>
       <c r="AW21" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX21" s="33"/>
@@ -7372,19 +7436,19 @@
         <v>5.4398148148148149E-3</v>
       </c>
       <c r="BC21" s="64">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.0763888888888889E-3</v>
       </c>
       <c r="BD21" s="33"/>
       <c r="BE21" s="33"/>
       <c r="BF21" s="64" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG21" s="33"/>
       <c r="BH21" s="33"/>
       <c r="BI21" s="64" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ21" s="33">
@@ -7394,25 +7458,25 @@
         <v>1.1743055555555555</v>
       </c>
       <c r="BL21" s="64">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.1699421296296295</v>
       </c>
       <c r="BM21" s="33"/>
       <c r="BN21" s="33"/>
       <c r="BO21" s="64" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BP21" s="33"/>
       <c r="BQ21" s="33"/>
       <c r="BR21" s="64" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS21" s="33"/>
       <c r="BT21" s="33"/>
       <c r="BU21" s="64" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BV21" s="33"/>
@@ -7479,15 +7543,11 @@
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
-      <c r="CZ21" s="33">
-        <v>1</v>
-      </c>
-      <c r="DA21" s="64">
-        <v>1.2305555555555556</v>
-      </c>
-      <c r="DB21" s="64">
+      <c r="CZ21" s="33"/>
+      <c r="DA21" s="64"/>
+      <c r="DB21" s="64" t="str">
         <f t="shared" si="23"/>
-        <v>1.2261921296296296</v>
+        <v>NA</v>
       </c>
       <c r="DC21" s="33">
         <v>1</v>
@@ -7528,14 +7588,14 @@
       <c r="DO21" s="33"/>
       <c r="DP21" s="64"/>
       <c r="DQ21" s="64" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>NA</v>
       </c>
       <c r="DR21" s="33"/>
     </row>
     <row r="22" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>132</v>
@@ -7585,7 +7645,10 @@
       <c r="P22" s="5">
         <v>2</v>
       </c>
-      <c r="Q22" s="5"/>
+      <c r="Q22" s="6">
+        <f t="shared" si="30"/>
+        <v>5.0694444444444486E-2</v>
+      </c>
       <c r="R22" s="5" t="s">
         <v>109</v>
       </c>
@@ -7610,7 +7673,7 @@
       <c r="AA22" s="63"/>
       <c r="AB22" s="63"/>
       <c r="AC22" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>5.1111111111111107E-2</v>
       </c>
       <c r="AD22" s="82">
@@ -7620,7 +7683,7 @@
         <v>6.4004629629629628E-3</v>
       </c>
       <c r="AF22" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.1064814814814811E-2</v>
       </c>
       <c r="AG22" s="21">
@@ -7631,20 +7694,16 @@
       </c>
       <c r="AI22" s="21"/>
       <c r="AJ22" s="33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK22" s="33">
-        <v>6</v>
-      </c>
-      <c r="AL22" s="33">
-        <v>6</v>
-      </c>
-      <c r="AM22" s="35">
-        <v>3.8541666666666668E-3</v>
-      </c>
-      <c r="AN22" s="64">
-        <f t="shared" si="32"/>
-        <v>2.0833333333333381E-4</v>
+        <v>7</v>
+      </c>
+      <c r="AL22" s="33"/>
+      <c r="AM22" s="35"/>
+      <c r="AN22" s="64" t="str">
+        <f t="shared" si="33"/>
+        <v>NA</v>
       </c>
       <c r="AO22" s="33">
         <v>3</v>
@@ -7653,19 +7712,23 @@
         <v>3.7384259259259263E-3</v>
       </c>
       <c r="AQ22" s="64">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>9.2592592592593333E-5</v>
       </c>
-      <c r="AR22" s="33"/>
-      <c r="AS22" s="33"/>
-      <c r="AT22" s="64" t="str">
-        <f t="shared" si="34"/>
-        <v>NA</v>
+      <c r="AR22" s="33">
+        <v>6</v>
+      </c>
+      <c r="AS22" s="35">
+        <v>3.8541666666666668E-3</v>
+      </c>
+      <c r="AT22" s="64">
+        <f t="shared" si="35"/>
+        <v>2.0833333333333381E-4</v>
       </c>
       <c r="AU22" s="33"/>
       <c r="AV22" s="33"/>
       <c r="AW22" s="64" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX22" s="33">
@@ -7685,19 +7748,19 @@
         <v>1.7361111111111112E-2</v>
       </c>
       <c r="BC22" s="64">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.3715277777777779E-2</v>
       </c>
       <c r="BD22" s="33"/>
       <c r="BE22" s="33"/>
       <c r="BF22" s="64" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BG22" s="33"/>
       <c r="BH22" s="33"/>
       <c r="BI22" s="64" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BJ22" s="33">
@@ -7707,25 +7770,25 @@
         <v>2.732638888888889E-2</v>
       </c>
       <c r="BL22" s="64">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2.3680555555555555E-2</v>
       </c>
       <c r="BM22" s="33"/>
       <c r="BN22" s="33"/>
       <c r="BO22" s="64" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BP22" s="33"/>
       <c r="BQ22" s="33"/>
       <c r="BR22" s="64" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BS22" s="33"/>
       <c r="BT22" s="33"/>
       <c r="BU22" s="64" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BV22" s="33"/>
@@ -7841,7 +7904,7 @@
         <v>1.8900462962962963E-2</v>
       </c>
       <c r="DQ22" s="64">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1.525462962962963E-2</v>
       </c>
       <c r="DR22" s="33"/>
